--- a/app/templates/zaisan.xlsx
+++ b/app/templates/zaisan.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_4D9D5B21493E81DBD874F033888855AD2103E15D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DEC2808-5B77-49A2-B65F-5CECB3342B67}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{BE6EC9E7-7EC8-4BFD-B462-13B4A8C35D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DE6BED0-863A-49E9-8780-913A35856726}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,9 +32,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="94">
   <si>
     <t>開始事件　事件番号</t>
+  </si>
+  <si>
+    <t>号</t>
+    <rPh sb="0" eb="1">
+      <t>ゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>】</t>
@@ -516,50 +523,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>３　生命保険、損害保険等（本人が契約者又は受取人になっているもの）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>初回報告（別紙のとおり）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>４　不動産（土地）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>５　不動産（建物）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>６　債権（貸付金、損害賠償金など）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>７　その他（自動車など）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>８　負債</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>９　遺産分割未了の相続財産（本人が相続人となっている遺産）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>該当財産なし )</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 前回報告から変化あり（別紙のとおり）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>前回報告から変化なし（</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve"> （３から９までの各項目についての記載方法）　</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -835,10 +798,6 @@
   </si>
   <si>
     <t>その他の種別は下欄の□にチェックを付し、種別の名称を記載してください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>該当なし )</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2004,7 +1963,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="413">
+  <cellXfs count="406">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2534,184 +2493,71 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2727,19 +2573,229 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -2747,8 +2803,131 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2767,63 +2946,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="184" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
@@ -2836,60 +2972,475 @@
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="183" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="18" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="18" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="18" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="18" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2905,655 +3456,49 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment shrinkToFit="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="18" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="18" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="18" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6080,10 +6025,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -6416,32 +6357,34 @@
       <c r="H2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="412"/>
-      <c r="J2" s="288"/>
-      <c r="K2" s="288"/>
-      <c r="L2" s="288"/>
-      <c r="M2" s="288"/>
-      <c r="N2" s="288"/>
-      <c r="O2" s="288"/>
-      <c r="P2" s="288"/>
-      <c r="Q2" s="288"/>
-      <c r="R2" s="288"/>
-      <c r="S2" s="29"/>
+      <c r="I2" s="391"/>
+      <c r="J2" s="393"/>
+      <c r="K2" s="393"/>
+      <c r="L2" s="393"/>
+      <c r="M2" s="393"/>
+      <c r="N2" s="393"/>
+      <c r="O2" s="393"/>
+      <c r="P2" s="393"/>
+      <c r="Q2" s="393"/>
+      <c r="R2" s="393"/>
+      <c r="S2" s="29" t="s">
+        <v>1</v>
+      </c>
       <c r="T2" s="29"/>
       <c r="U2" s="21"/>
       <c r="V2" s="129" t="s">
-        <v>58</v>
-      </c>
-      <c r="W2" s="276"/>
-      <c r="X2" s="276"/>
-      <c r="Y2" s="277"/>
-      <c r="Z2" s="278"/>
-      <c r="AA2" s="278"/>
-      <c r="AB2" s="278"/>
-      <c r="AC2" s="278"/>
-      <c r="AD2" s="278"/>
+        <v>59</v>
+      </c>
+      <c r="W2" s="163"/>
+      <c r="X2" s="163"/>
+      <c r="Y2" s="164"/>
+      <c r="Z2" s="165"/>
+      <c r="AA2" s="165"/>
+      <c r="AB2" s="165"/>
+      <c r="AC2" s="165"/>
+      <c r="AD2" s="165"/>
       <c r="AE2" s="23" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6459,17 +6402,17 @@
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
       <c r="N4" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="O4" s="281"/>
-      <c r="P4" s="282"/>
-      <c r="Q4" s="282"/>
-      <c r="R4" s="282"/>
-      <c r="S4" s="282"/>
-      <c r="T4" s="282"/>
-      <c r="U4" s="282"/>
+        <v>71</v>
+      </c>
+      <c r="O4" s="173"/>
+      <c r="P4" s="174"/>
+      <c r="Q4" s="174"/>
+      <c r="R4" s="174"/>
+      <c r="S4" s="174"/>
+      <c r="T4" s="174"/>
+      <c r="U4" s="174"/>
       <c r="V4" s="80" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4" s="18"/>
       <c r="X4" s="17"/>
@@ -6518,27 +6461,28 @@
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
-      <c r="I6" s="248"/>
-      <c r="J6" s="249"/>
-      <c r="K6" s="249"/>
-      <c r="L6" s="249"/>
-      <c r="M6" s="249"/>
-      <c r="N6" s="249"/>
-      <c r="O6" s="249"/>
-      <c r="P6" s="249"/>
+      <c r="I6" s="392"/>
+      <c r="J6" s="392"/>
+      <c r="K6" s="392"/>
+      <c r="L6" s="392"/>
+      <c r="M6" s="392"/>
+      <c r="N6" s="392"/>
+      <c r="O6" s="392"/>
+      <c r="P6" s="392"/>
+      <c r="Q6" s="392"/>
       <c r="S6" s="100"/>
       <c r="U6" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="V6" s="279"/>
-      <c r="W6" s="280"/>
-      <c r="X6" s="280"/>
-      <c r="Y6" s="280"/>
-      <c r="Z6" s="280"/>
-      <c r="AA6" s="280"/>
-      <c r="AB6" s="280"/>
+        <v>93</v>
+      </c>
+      <c r="V6" s="171"/>
+      <c r="W6" s="172"/>
+      <c r="X6" s="172"/>
+      <c r="Y6" s="172"/>
+      <c r="Z6" s="172"/>
+      <c r="AA6" s="172"/>
+      <c r="AB6" s="172"/>
       <c r="AD6" s="20" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -6572,40 +6516,40 @@
       <c r="AE7" s="23"/>
     </row>
     <row r="8" spans="1:36" s="27" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="283" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="284"/>
-      <c r="C8" s="284"/>
-      <c r="D8" s="284"/>
-      <c r="E8" s="284"/>
-      <c r="F8" s="284"/>
-      <c r="G8" s="284"/>
-      <c r="H8" s="284"/>
-      <c r="I8" s="284"/>
-      <c r="J8" s="284"/>
-      <c r="K8" s="284"/>
-      <c r="L8" s="284"/>
-      <c r="M8" s="284"/>
-      <c r="N8" s="284"/>
-      <c r="O8" s="284"/>
-      <c r="P8" s="284"/>
-      <c r="Q8" s="284"/>
-      <c r="R8" s="284"/>
-      <c r="S8" s="284"/>
-      <c r="T8" s="284"/>
-      <c r="U8" s="284"/>
-      <c r="V8" s="284"/>
-      <c r="W8" s="284"/>
-      <c r="X8" s="284"/>
-      <c r="Y8" s="284"/>
-      <c r="Z8" s="284"/>
-      <c r="AA8" s="284"/>
-      <c r="AB8" s="284"/>
-      <c r="AC8" s="284"/>
-      <c r="AD8" s="284"/>
-      <c r="AE8" s="284"/>
-      <c r="AF8" s="284"/>
+      <c r="A8" s="175" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="176"/>
+      <c r="C8" s="176"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="176"/>
+      <c r="K8" s="176"/>
+      <c r="L8" s="176"/>
+      <c r="M8" s="176"/>
+      <c r="N8" s="176"/>
+      <c r="O8" s="176"/>
+      <c r="P8" s="176"/>
+      <c r="Q8" s="176"/>
+      <c r="R8" s="176"/>
+      <c r="S8" s="176"/>
+      <c r="T8" s="176"/>
+      <c r="U8" s="176"/>
+      <c r="V8" s="176"/>
+      <c r="W8" s="176"/>
+      <c r="X8" s="176"/>
+      <c r="Y8" s="176"/>
+      <c r="Z8" s="176"/>
+      <c r="AA8" s="176"/>
+      <c r="AB8" s="176"/>
+      <c r="AC8" s="176"/>
+      <c r="AD8" s="176"/>
+      <c r="AE8" s="176"/>
+      <c r="AF8" s="176"/>
       <c r="AG8" s="25"/>
       <c r="AH8" s="25"/>
       <c r="AI8" s="25"/>
@@ -6650,160 +6594,160 @@
       <c r="AJ9" s="26"/>
     </row>
     <row r="10" spans="1:36" s="31" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="285" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="284"/>
-      <c r="C10" s="284"/>
-      <c r="D10" s="284"/>
-      <c r="E10" s="284"/>
-      <c r="F10" s="284"/>
-      <c r="G10" s="284"/>
-      <c r="H10" s="284"/>
-      <c r="I10" s="284"/>
-      <c r="J10" s="284"/>
-      <c r="K10" s="284"/>
-      <c r="L10" s="284"/>
-      <c r="M10" s="284"/>
-      <c r="N10" s="284"/>
-      <c r="O10" s="284"/>
-      <c r="P10" s="284"/>
-      <c r="Q10" s="284"/>
-      <c r="R10" s="284"/>
-      <c r="S10" s="284"/>
-      <c r="T10" s="284"/>
-      <c r="U10" s="284"/>
-      <c r="V10" s="284"/>
-      <c r="W10" s="284"/>
-      <c r="X10" s="284"/>
-      <c r="Y10" s="284"/>
-      <c r="Z10" s="284"/>
-      <c r="AA10" s="284"/>
-      <c r="AB10" s="284"/>
-      <c r="AC10" s="284"/>
-      <c r="AD10" s="284"/>
-      <c r="AE10" s="284"/>
-      <c r="AF10" s="284"/>
+      <c r="A10" s="177" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="176"/>
+      <c r="C10" s="176"/>
+      <c r="D10" s="176"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="176"/>
+      <c r="G10" s="176"/>
+      <c r="H10" s="176"/>
+      <c r="I10" s="176"/>
+      <c r="J10" s="176"/>
+      <c r="K10" s="176"/>
+      <c r="L10" s="176"/>
+      <c r="M10" s="176"/>
+      <c r="N10" s="176"/>
+      <c r="O10" s="176"/>
+      <c r="P10" s="176"/>
+      <c r="Q10" s="176"/>
+      <c r="R10" s="176"/>
+      <c r="S10" s="176"/>
+      <c r="T10" s="176"/>
+      <c r="U10" s="176"/>
+      <c r="V10" s="176"/>
+      <c r="W10" s="176"/>
+      <c r="X10" s="176"/>
+      <c r="Y10" s="176"/>
+      <c r="Z10" s="176"/>
+      <c r="AA10" s="176"/>
+      <c r="AB10" s="176"/>
+      <c r="AC10" s="176"/>
+      <c r="AD10" s="176"/>
+      <c r="AE10" s="176"/>
+      <c r="AF10" s="176"/>
       <c r="AG10" s="29"/>
       <c r="AH10" s="29"/>
       <c r="AI10" s="29"/>
       <c r="AJ10" s="30"/>
     </row>
     <row r="11" spans="1:36" s="31" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="285" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="221"/>
-      <c r="C11" s="221"/>
-      <c r="D11" s="221"/>
-      <c r="E11" s="221"/>
-      <c r="F11" s="221"/>
-      <c r="G11" s="221"/>
-      <c r="H11" s="221"/>
-      <c r="I11" s="221"/>
-      <c r="J11" s="221"/>
-      <c r="K11" s="221"/>
-      <c r="L11" s="221"/>
-      <c r="M11" s="221"/>
-      <c r="N11" s="221"/>
-      <c r="O11" s="221"/>
-      <c r="P11" s="221"/>
-      <c r="Q11" s="221"/>
-      <c r="R11" s="221"/>
-      <c r="S11" s="221"/>
-      <c r="T11" s="221"/>
-      <c r="U11" s="221"/>
-      <c r="V11" s="221"/>
-      <c r="W11" s="221"/>
-      <c r="X11" s="221"/>
-      <c r="Y11" s="221"/>
-      <c r="Z11" s="221"/>
-      <c r="AA11" s="221"/>
-      <c r="AB11" s="221"/>
-      <c r="AC11" s="221"/>
-      <c r="AD11" s="221"/>
-      <c r="AE11" s="221"/>
-      <c r="AF11" s="221"/>
+      <c r="A11" s="177" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="150"/>
+      <c r="C11" s="150"/>
+      <c r="D11" s="150"/>
+      <c r="E11" s="150"/>
+      <c r="F11" s="150"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="150"/>
+      <c r="I11" s="150"/>
+      <c r="J11" s="150"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="150"/>
+      <c r="N11" s="150"/>
+      <c r="O11" s="150"/>
+      <c r="P11" s="150"/>
+      <c r="Q11" s="150"/>
+      <c r="R11" s="150"/>
+      <c r="S11" s="150"/>
+      <c r="T11" s="150"/>
+      <c r="U11" s="150"/>
+      <c r="V11" s="150"/>
+      <c r="W11" s="150"/>
+      <c r="X11" s="150"/>
+      <c r="Y11" s="150"/>
+      <c r="Z11" s="150"/>
+      <c r="AA11" s="150"/>
+      <c r="AB11" s="150"/>
+      <c r="AC11" s="150"/>
+      <c r="AD11" s="150"/>
+      <c r="AE11" s="150"/>
+      <c r="AF11" s="150"/>
       <c r="AG11" s="29"/>
       <c r="AH11" s="29"/>
       <c r="AI11" s="29"/>
       <c r="AJ11" s="30"/>
     </row>
     <row r="12" spans="1:36" s="31" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="285" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" s="284"/>
-      <c r="C12" s="284"/>
-      <c r="D12" s="284"/>
-      <c r="E12" s="284"/>
-      <c r="F12" s="284"/>
-      <c r="G12" s="284"/>
-      <c r="H12" s="284"/>
-      <c r="I12" s="284"/>
-      <c r="J12" s="284"/>
-      <c r="K12" s="284"/>
-      <c r="L12" s="284"/>
-      <c r="M12" s="284"/>
-      <c r="N12" s="284"/>
-      <c r="O12" s="284"/>
-      <c r="P12" s="284"/>
-      <c r="Q12" s="284"/>
-      <c r="R12" s="284"/>
-      <c r="S12" s="284"/>
-      <c r="T12" s="284"/>
-      <c r="U12" s="284"/>
-      <c r="V12" s="284"/>
-      <c r="W12" s="284"/>
-      <c r="X12" s="284"/>
-      <c r="Y12" s="284"/>
-      <c r="Z12" s="284"/>
-      <c r="AA12" s="284"/>
-      <c r="AB12" s="284"/>
-      <c r="AC12" s="284"/>
-      <c r="AD12" s="284"/>
-      <c r="AE12" s="284"/>
-      <c r="AF12" s="284"/>
+      <c r="A12" s="177" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="176"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="176"/>
+      <c r="K12" s="176"/>
+      <c r="L12" s="176"/>
+      <c r="M12" s="176"/>
+      <c r="N12" s="176"/>
+      <c r="O12" s="176"/>
+      <c r="P12" s="176"/>
+      <c r="Q12" s="176"/>
+      <c r="R12" s="176"/>
+      <c r="S12" s="176"/>
+      <c r="T12" s="176"/>
+      <c r="U12" s="176"/>
+      <c r="V12" s="176"/>
+      <c r="W12" s="176"/>
+      <c r="X12" s="176"/>
+      <c r="Y12" s="176"/>
+      <c r="Z12" s="176"/>
+      <c r="AA12" s="176"/>
+      <c r="AB12" s="176"/>
+      <c r="AC12" s="176"/>
+      <c r="AD12" s="176"/>
+      <c r="AE12" s="176"/>
+      <c r="AF12" s="176"/>
       <c r="AG12" s="29"/>
       <c r="AH12" s="29"/>
       <c r="AI12" s="29"/>
       <c r="AJ12" s="30"/>
     </row>
     <row r="13" spans="1:36" s="31" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="285" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="284"/>
-      <c r="C13" s="284"/>
-      <c r="D13" s="284"/>
-      <c r="E13" s="284"/>
-      <c r="F13" s="284"/>
-      <c r="G13" s="284"/>
-      <c r="H13" s="284"/>
-      <c r="I13" s="284"/>
-      <c r="J13" s="284"/>
-      <c r="K13" s="284"/>
-      <c r="L13" s="284"/>
-      <c r="M13" s="284"/>
-      <c r="N13" s="284"/>
-      <c r="O13" s="284"/>
-      <c r="P13" s="284"/>
-      <c r="Q13" s="284"/>
-      <c r="R13" s="284"/>
-      <c r="S13" s="284"/>
-      <c r="T13" s="284"/>
-      <c r="U13" s="284"/>
-      <c r="V13" s="284"/>
-      <c r="W13" s="284"/>
-      <c r="X13" s="284"/>
-      <c r="Y13" s="284"/>
-      <c r="Z13" s="284"/>
-      <c r="AA13" s="284"/>
-      <c r="AB13" s="284"/>
-      <c r="AC13" s="284"/>
-      <c r="AD13" s="284"/>
-      <c r="AE13" s="284"/>
-      <c r="AF13" s="284"/>
+      <c r="A13" s="177" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="176"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="176"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="176"/>
+      <c r="K13" s="176"/>
+      <c r="L13" s="176"/>
+      <c r="M13" s="176"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="176"/>
+      <c r="Q13" s="176"/>
+      <c r="R13" s="176"/>
+      <c r="S13" s="176"/>
+      <c r="T13" s="176"/>
+      <c r="U13" s="176"/>
+      <c r="V13" s="176"/>
+      <c r="W13" s="176"/>
+      <c r="X13" s="176"/>
+      <c r="Y13" s="176"/>
+      <c r="Z13" s="176"/>
+      <c r="AA13" s="176"/>
+      <c r="AB13" s="176"/>
+      <c r="AC13" s="176"/>
+      <c r="AD13" s="176"/>
+      <c r="AE13" s="176"/>
+      <c r="AF13" s="176"/>
       <c r="AG13" s="29"/>
       <c r="AH13" s="29"/>
       <c r="AI13" s="29"/>
@@ -6811,7 +6755,7 @@
     </row>
     <row r="14" spans="1:36" s="31" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="109" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B14" s="107"/>
       <c r="C14" s="107"/>
@@ -6888,40 +6832,40 @@
       <c r="AJ15" s="30"/>
     </row>
     <row r="16" spans="1:36" s="31" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="285" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="284"/>
-      <c r="C16" s="284"/>
-      <c r="D16" s="284"/>
-      <c r="E16" s="284"/>
-      <c r="F16" s="284"/>
-      <c r="G16" s="284"/>
-      <c r="H16" s="284"/>
-      <c r="I16" s="284"/>
-      <c r="J16" s="284"/>
-      <c r="K16" s="284"/>
-      <c r="L16" s="284"/>
-      <c r="M16" s="284"/>
-      <c r="N16" s="284"/>
-      <c r="O16" s="284"/>
-      <c r="P16" s="284"/>
-      <c r="Q16" s="284"/>
-      <c r="R16" s="284"/>
-      <c r="S16" s="284"/>
-      <c r="T16" s="284"/>
-      <c r="U16" s="284"/>
-      <c r="V16" s="284"/>
-      <c r="W16" s="284"/>
-      <c r="X16" s="284"/>
-      <c r="Y16" s="284"/>
-      <c r="Z16" s="284"/>
-      <c r="AA16" s="284"/>
-      <c r="AB16" s="284"/>
-      <c r="AC16" s="284"/>
-      <c r="AD16" s="284"/>
-      <c r="AE16" s="284"/>
-      <c r="AF16" s="284"/>
+      <c r="A16" s="177" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="176"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="176"/>
+      <c r="E16" s="176"/>
+      <c r="F16" s="176"/>
+      <c r="G16" s="176"/>
+      <c r="H16" s="176"/>
+      <c r="I16" s="176"/>
+      <c r="J16" s="176"/>
+      <c r="K16" s="176"/>
+      <c r="L16" s="176"/>
+      <c r="M16" s="176"/>
+      <c r="N16" s="176"/>
+      <c r="O16" s="176"/>
+      <c r="P16" s="176"/>
+      <c r="Q16" s="176"/>
+      <c r="R16" s="176"/>
+      <c r="S16" s="176"/>
+      <c r="T16" s="176"/>
+      <c r="U16" s="176"/>
+      <c r="V16" s="176"/>
+      <c r="W16" s="176"/>
+      <c r="X16" s="176"/>
+      <c r="Y16" s="176"/>
+      <c r="Z16" s="176"/>
+      <c r="AA16" s="176"/>
+      <c r="AB16" s="176"/>
+      <c r="AC16" s="176"/>
+      <c r="AD16" s="176"/>
+      <c r="AE16" s="176"/>
+      <c r="AF16" s="176"/>
       <c r="AG16" s="29"/>
       <c r="AH16" s="29"/>
       <c r="AI16" s="29"/>
@@ -6930,7 +6874,7 @@
     <row r="17" spans="1:36" s="31" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="32"/>
       <c r="B17" s="33" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="23"/>
@@ -7008,7 +6952,7 @@
     <row r="19" spans="1:36" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="32"/>
       <c r="B19" s="34" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="34"/>
       <c r="D19" s="34"/>
@@ -7047,22 +6991,22 @@
     </row>
     <row r="20" spans="1:36" s="31" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="32"/>
-      <c r="B20" s="217" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="218"/>
+      <c r="B20" s="169" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="170"/>
       <c r="D20" s="35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="35"/>
       <c r="F20" s="35"/>
       <c r="G20" s="35"/>
       <c r="H20" s="35"/>
       <c r="I20" s="141" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="35"/>
       <c r="L20" s="35"/>
@@ -7071,10 +7015,10 @@
       <c r="O20" s="35"/>
       <c r="P20" s="35"/>
       <c r="Q20" s="141" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R20" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S20" s="100"/>
       <c r="T20" s="23"/>
@@ -7097,39 +7041,39 @@
     </row>
     <row r="21" spans="1:36" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="32"/>
-      <c r="B21" s="286" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="287"/>
-      <c r="D21" s="287"/>
-      <c r="E21" s="287"/>
-      <c r="F21" s="287"/>
-      <c r="G21" s="287"/>
-      <c r="H21" s="287"/>
-      <c r="I21" s="287"/>
-      <c r="J21" s="287"/>
-      <c r="K21" s="287"/>
-      <c r="L21" s="287"/>
-      <c r="M21" s="287"/>
-      <c r="N21" s="287"/>
-      <c r="O21" s="287"/>
-      <c r="P21" s="287"/>
-      <c r="Q21" s="287"/>
-      <c r="R21" s="287"/>
-      <c r="S21" s="287"/>
-      <c r="T21" s="287"/>
-      <c r="U21" s="287"/>
-      <c r="V21" s="287"/>
-      <c r="W21" s="287"/>
-      <c r="X21" s="287"/>
-      <c r="Y21" s="287"/>
-      <c r="Z21" s="287"/>
-      <c r="AA21" s="287"/>
-      <c r="AB21" s="287"/>
-      <c r="AC21" s="287"/>
-      <c r="AD21" s="287"/>
-      <c r="AE21" s="287"/>
-      <c r="AF21" s="287"/>
+      <c r="B21" s="178" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="179"/>
+      <c r="D21" s="179"/>
+      <c r="E21" s="179"/>
+      <c r="F21" s="179"/>
+      <c r="G21" s="179"/>
+      <c r="H21" s="179"/>
+      <c r="I21" s="179"/>
+      <c r="J21" s="179"/>
+      <c r="K21" s="179"/>
+      <c r="L21" s="179"/>
+      <c r="M21" s="179"/>
+      <c r="N21" s="179"/>
+      <c r="O21" s="179"/>
+      <c r="P21" s="179"/>
+      <c r="Q21" s="179"/>
+      <c r="R21" s="179"/>
+      <c r="S21" s="179"/>
+      <c r="T21" s="179"/>
+      <c r="U21" s="179"/>
+      <c r="V21" s="179"/>
+      <c r="W21" s="179"/>
+      <c r="X21" s="179"/>
+      <c r="Y21" s="179"/>
+      <c r="Z21" s="179"/>
+      <c r="AA21" s="179"/>
+      <c r="AB21" s="179"/>
+      <c r="AC21" s="179"/>
+      <c r="AD21" s="179"/>
+      <c r="AE21" s="179"/>
+      <c r="AF21" s="179"/>
       <c r="AG21" s="30"/>
       <c r="AH21" s="30"/>
       <c r="AI21" s="30"/>
@@ -7138,7 +7082,7 @@
     <row r="22" spans="1:36" s="31" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="32"/>
       <c r="B22" s="102" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C22" s="103"/>
       <c r="D22" s="103"/>
@@ -7214,473 +7158,473 @@
     <row r="24" spans="1:36" s="31" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="32"/>
       <c r="B24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="193" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="194"/>
-      <c r="E24" s="194"/>
-      <c r="F24" s="194"/>
-      <c r="G24" s="194"/>
-      <c r="H24" s="195"/>
-      <c r="I24" s="193" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="J24" s="194"/>
-      <c r="K24" s="194"/>
-      <c r="L24" s="195"/>
-      <c r="M24" s="193" t="s">
+      <c r="D24" s="167"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="167"/>
+      <c r="H24" s="168"/>
+      <c r="I24" s="166" t="s">
         <v>41</v>
       </c>
-      <c r="N24" s="194"/>
-      <c r="O24" s="194"/>
-      <c r="P24" s="195"/>
-      <c r="Q24" s="193" t="s">
+      <c r="J24" s="167"/>
+      <c r="K24" s="167"/>
+      <c r="L24" s="168"/>
+      <c r="M24" s="166" t="s">
         <v>42</v>
       </c>
-      <c r="R24" s="194"/>
-      <c r="S24" s="194"/>
-      <c r="T24" s="195"/>
-      <c r="U24" s="193" t="s">
+      <c r="N24" s="167"/>
+      <c r="O24" s="167"/>
+      <c r="P24" s="168"/>
+      <c r="Q24" s="166" t="s">
         <v>43</v>
       </c>
-      <c r="V24" s="194"/>
-      <c r="W24" s="195"/>
-      <c r="X24" s="193" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y24" s="194"/>
-      <c r="Z24" s="194"/>
-      <c r="AA24" s="195"/>
-      <c r="AB24" s="193" t="s">
+      <c r="R24" s="167"/>
+      <c r="S24" s="167"/>
+      <c r="T24" s="168"/>
+      <c r="U24" s="166" t="s">
         <v>44</v>
       </c>
-      <c r="AC24" s="194"/>
-      <c r="AD24" s="194"/>
-      <c r="AE24" s="195"/>
+      <c r="V24" s="167"/>
+      <c r="W24" s="168"/>
+      <c r="X24" s="166" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y24" s="167"/>
+      <c r="Z24" s="167"/>
+      <c r="AA24" s="168"/>
+      <c r="AB24" s="166" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC24" s="167"/>
+      <c r="AD24" s="167"/>
+      <c r="AE24" s="168"/>
       <c r="AF24" s="77" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG24" s="30"/>
       <c r="AH24" s="30"/>
     </row>
     <row r="25" spans="1:36" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="118"/>
-      <c r="B25" s="268">
+      <c r="B25" s="218">
         <v>1</v>
       </c>
-      <c r="C25" s="256"/>
-      <c r="D25" s="257"/>
-      <c r="E25" s="257"/>
-      <c r="F25" s="257"/>
-      <c r="G25" s="257"/>
-      <c r="H25" s="258"/>
-      <c r="I25" s="256"/>
-      <c r="J25" s="257"/>
-      <c r="K25" s="257"/>
-      <c r="L25" s="258"/>
-      <c r="M25" s="273"/>
-      <c r="N25" s="274"/>
-      <c r="O25" s="274"/>
-      <c r="P25" s="275"/>
-      <c r="Q25" s="259"/>
-      <c r="R25" s="260"/>
-      <c r="S25" s="260"/>
-      <c r="T25" s="261"/>
-      <c r="U25" s="262"/>
-      <c r="V25" s="263"/>
-      <c r="W25" s="264"/>
-      <c r="X25" s="270"/>
-      <c r="Y25" s="271"/>
-      <c r="Z25" s="271"/>
-      <c r="AA25" s="272"/>
-      <c r="AB25" s="256"/>
-      <c r="AC25" s="257"/>
-      <c r="AD25" s="257"/>
-      <c r="AE25" s="258"/>
-      <c r="AF25" s="246" t="s">
-        <v>5</v>
+      <c r="C25" s="206"/>
+      <c r="D25" s="207"/>
+      <c r="E25" s="207"/>
+      <c r="F25" s="207"/>
+      <c r="G25" s="207"/>
+      <c r="H25" s="208"/>
+      <c r="I25" s="206"/>
+      <c r="J25" s="207"/>
+      <c r="K25" s="207"/>
+      <c r="L25" s="208"/>
+      <c r="M25" s="394"/>
+      <c r="N25" s="395"/>
+      <c r="O25" s="395"/>
+      <c r="P25" s="396"/>
+      <c r="Q25" s="209"/>
+      <c r="R25" s="210"/>
+      <c r="S25" s="210"/>
+      <c r="T25" s="211"/>
+      <c r="U25" s="212"/>
+      <c r="V25" s="213"/>
+      <c r="W25" s="214"/>
+      <c r="X25" s="220"/>
+      <c r="Y25" s="221"/>
+      <c r="Z25" s="221"/>
+      <c r="AA25" s="222"/>
+      <c r="AB25" s="206"/>
+      <c r="AC25" s="207"/>
+      <c r="AD25" s="207"/>
+      <c r="AE25" s="208"/>
+      <c r="AF25" s="232" t="s">
+        <v>6</v>
       </c>
       <c r="AG25" s="119"/>
       <c r="AH25" s="119"/>
     </row>
     <row r="26" spans="1:36" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="118"/>
-      <c r="B26" s="269"/>
-      <c r="C26" s="155"/>
-      <c r="D26" s="156"/>
-      <c r="E26" s="156"/>
-      <c r="F26" s="156"/>
-      <c r="G26" s="156"/>
-      <c r="H26" s="157"/>
-      <c r="I26" s="155"/>
-      <c r="J26" s="156"/>
-      <c r="K26" s="156"/>
-      <c r="L26" s="157"/>
-      <c r="M26" s="240"/>
-      <c r="N26" s="241"/>
-      <c r="O26" s="241"/>
-      <c r="P26" s="242"/>
-      <c r="Q26" s="161"/>
-      <c r="R26" s="162"/>
-      <c r="S26" s="162"/>
-      <c r="T26" s="163"/>
-      <c r="U26" s="265"/>
-      <c r="V26" s="266"/>
-      <c r="W26" s="267"/>
-      <c r="X26" s="173"/>
-      <c r="Y26" s="174"/>
-      <c r="Z26" s="174"/>
-      <c r="AA26" s="175"/>
-      <c r="AB26" s="155"/>
-      <c r="AC26" s="156"/>
-      <c r="AD26" s="156"/>
-      <c r="AE26" s="157"/>
-      <c r="AF26" s="247"/>
+      <c r="B26" s="219"/>
+      <c r="C26" s="185"/>
+      <c r="D26" s="186"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="186"/>
+      <c r="G26" s="186"/>
+      <c r="H26" s="187"/>
+      <c r="I26" s="185"/>
+      <c r="J26" s="186"/>
+      <c r="K26" s="186"/>
+      <c r="L26" s="187"/>
+      <c r="M26" s="397"/>
+      <c r="N26" s="398"/>
+      <c r="O26" s="398"/>
+      <c r="P26" s="399"/>
+      <c r="Q26" s="191"/>
+      <c r="R26" s="192"/>
+      <c r="S26" s="192"/>
+      <c r="T26" s="193"/>
+      <c r="U26" s="215"/>
+      <c r="V26" s="216"/>
+      <c r="W26" s="217"/>
+      <c r="X26" s="203"/>
+      <c r="Y26" s="204"/>
+      <c r="Z26" s="204"/>
+      <c r="AA26" s="205"/>
+      <c r="AB26" s="185"/>
+      <c r="AC26" s="186"/>
+      <c r="AD26" s="186"/>
+      <c r="AE26" s="187"/>
+      <c r="AF26" s="233"/>
       <c r="AG26" s="119"/>
       <c r="AH26" s="119"/>
     </row>
     <row r="27" spans="1:36" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="118"/>
-      <c r="B27" s="150">
+      <c r="B27" s="180">
         <v>2</v>
       </c>
-      <c r="C27" s="152"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="153"/>
-      <c r="G27" s="153"/>
-      <c r="H27" s="154"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="153"/>
-      <c r="L27" s="154"/>
-      <c r="M27" s="237"/>
-      <c r="N27" s="238"/>
-      <c r="O27" s="238"/>
-      <c r="P27" s="239"/>
-      <c r="Q27" s="158"/>
-      <c r="R27" s="159"/>
-      <c r="S27" s="159"/>
-      <c r="T27" s="160"/>
-      <c r="U27" s="164"/>
-      <c r="V27" s="165"/>
-      <c r="W27" s="166"/>
-      <c r="X27" s="170"/>
-      <c r="Y27" s="171"/>
-      <c r="Z27" s="171"/>
-      <c r="AA27" s="172"/>
-      <c r="AB27" s="152"/>
-      <c r="AC27" s="153"/>
-      <c r="AD27" s="153"/>
-      <c r="AE27" s="154"/>
-      <c r="AF27" s="229" t="s">
-        <v>5</v>
+      <c r="C27" s="182"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="183"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="183"/>
+      <c r="H27" s="184"/>
+      <c r="I27" s="182"/>
+      <c r="J27" s="183"/>
+      <c r="K27" s="183"/>
+      <c r="L27" s="184"/>
+      <c r="M27" s="182"/>
+      <c r="N27" s="183"/>
+      <c r="O27" s="183"/>
+      <c r="P27" s="184"/>
+      <c r="Q27" s="188"/>
+      <c r="R27" s="189"/>
+      <c r="S27" s="189"/>
+      <c r="T27" s="190"/>
+      <c r="U27" s="194"/>
+      <c r="V27" s="195"/>
+      <c r="W27" s="196"/>
+      <c r="X27" s="200"/>
+      <c r="Y27" s="201"/>
+      <c r="Z27" s="201"/>
+      <c r="AA27" s="202"/>
+      <c r="AB27" s="182"/>
+      <c r="AC27" s="183"/>
+      <c r="AD27" s="183"/>
+      <c r="AE27" s="184"/>
+      <c r="AF27" s="234" t="s">
+        <v>6</v>
       </c>
       <c r="AG27" s="119"/>
       <c r="AH27" s="119"/>
     </row>
     <row r="28" spans="1:36" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="118"/>
-      <c r="B28" s="151"/>
-      <c r="C28" s="155"/>
-      <c r="D28" s="156"/>
-      <c r="E28" s="156"/>
-      <c r="F28" s="156"/>
-      <c r="G28" s="156"/>
-      <c r="H28" s="157"/>
-      <c r="I28" s="155"/>
-      <c r="J28" s="156"/>
-      <c r="K28" s="156"/>
-      <c r="L28" s="157"/>
-      <c r="M28" s="240"/>
-      <c r="N28" s="241"/>
-      <c r="O28" s="241"/>
-      <c r="P28" s="242"/>
-      <c r="Q28" s="161"/>
-      <c r="R28" s="162"/>
-      <c r="S28" s="162"/>
-      <c r="T28" s="163"/>
-      <c r="U28" s="167"/>
-      <c r="V28" s="168"/>
-      <c r="W28" s="169"/>
-      <c r="X28" s="173"/>
-      <c r="Y28" s="174"/>
-      <c r="Z28" s="174"/>
-      <c r="AA28" s="175"/>
-      <c r="AB28" s="155"/>
-      <c r="AC28" s="156"/>
-      <c r="AD28" s="156"/>
-      <c r="AE28" s="157"/>
-      <c r="AF28" s="230"/>
+      <c r="B28" s="181"/>
+      <c r="C28" s="185"/>
+      <c r="D28" s="186"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="186"/>
+      <c r="G28" s="186"/>
+      <c r="H28" s="187"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="186"/>
+      <c r="K28" s="186"/>
+      <c r="L28" s="187"/>
+      <c r="M28" s="185"/>
+      <c r="N28" s="186"/>
+      <c r="O28" s="186"/>
+      <c r="P28" s="187"/>
+      <c r="Q28" s="191"/>
+      <c r="R28" s="192"/>
+      <c r="S28" s="192"/>
+      <c r="T28" s="193"/>
+      <c r="U28" s="197"/>
+      <c r="V28" s="198"/>
+      <c r="W28" s="199"/>
+      <c r="X28" s="203"/>
+      <c r="Y28" s="204"/>
+      <c r="Z28" s="204"/>
+      <c r="AA28" s="205"/>
+      <c r="AB28" s="185"/>
+      <c r="AC28" s="186"/>
+      <c r="AD28" s="186"/>
+      <c r="AE28" s="187"/>
+      <c r="AF28" s="235"/>
       <c r="AG28" s="119"/>
       <c r="AH28" s="119"/>
     </row>
     <row r="29" spans="1:36" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="118"/>
-      <c r="B29" s="150">
+      <c r="B29" s="180">
         <v>3</v>
       </c>
-      <c r="C29" s="152"/>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
-      <c r="F29" s="153"/>
-      <c r="G29" s="153"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="152"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="153"/>
-      <c r="L29" s="154"/>
-      <c r="M29" s="237"/>
-      <c r="N29" s="238"/>
-      <c r="O29" s="238"/>
-      <c r="P29" s="239"/>
-      <c r="Q29" s="158"/>
-      <c r="R29" s="159"/>
-      <c r="S29" s="159"/>
-      <c r="T29" s="160"/>
-      <c r="U29" s="164"/>
-      <c r="V29" s="165"/>
-      <c r="W29" s="166"/>
-      <c r="X29" s="170"/>
-      <c r="Y29" s="171"/>
-      <c r="Z29" s="171"/>
-      <c r="AA29" s="172"/>
-      <c r="AB29" s="152"/>
-      <c r="AC29" s="153"/>
-      <c r="AD29" s="153"/>
-      <c r="AE29" s="154"/>
-      <c r="AF29" s="229" t="s">
-        <v>5</v>
+      <c r="C29" s="182"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="183"/>
+      <c r="F29" s="183"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="182"/>
+      <c r="J29" s="183"/>
+      <c r="K29" s="183"/>
+      <c r="L29" s="184"/>
+      <c r="M29" s="182"/>
+      <c r="N29" s="183"/>
+      <c r="O29" s="183"/>
+      <c r="P29" s="184"/>
+      <c r="Q29" s="188"/>
+      <c r="R29" s="189"/>
+      <c r="S29" s="189"/>
+      <c r="T29" s="190"/>
+      <c r="U29" s="194"/>
+      <c r="V29" s="195"/>
+      <c r="W29" s="196"/>
+      <c r="X29" s="200"/>
+      <c r="Y29" s="201"/>
+      <c r="Z29" s="201"/>
+      <c r="AA29" s="202"/>
+      <c r="AB29" s="182"/>
+      <c r="AC29" s="183"/>
+      <c r="AD29" s="183"/>
+      <c r="AE29" s="184"/>
+      <c r="AF29" s="234" t="s">
+        <v>6</v>
       </c>
       <c r="AG29" s="119"/>
       <c r="AH29" s="119"/>
     </row>
     <row r="30" spans="1:36" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="118"/>
-      <c r="B30" s="151"/>
-      <c r="C30" s="155"/>
-      <c r="D30" s="156"/>
-      <c r="E30" s="156"/>
-      <c r="F30" s="156"/>
-      <c r="G30" s="156"/>
-      <c r="H30" s="157"/>
-      <c r="I30" s="155"/>
-      <c r="J30" s="156"/>
-      <c r="K30" s="156"/>
-      <c r="L30" s="157"/>
-      <c r="M30" s="240"/>
-      <c r="N30" s="241"/>
-      <c r="O30" s="241"/>
-      <c r="P30" s="242"/>
-      <c r="Q30" s="161"/>
-      <c r="R30" s="162"/>
-      <c r="S30" s="162"/>
-      <c r="T30" s="163"/>
-      <c r="U30" s="167"/>
-      <c r="V30" s="168"/>
-      <c r="W30" s="169"/>
-      <c r="X30" s="173"/>
-      <c r="Y30" s="174"/>
-      <c r="Z30" s="174"/>
-      <c r="AA30" s="175"/>
-      <c r="AB30" s="155"/>
-      <c r="AC30" s="156"/>
-      <c r="AD30" s="156"/>
-      <c r="AE30" s="157"/>
-      <c r="AF30" s="230"/>
+      <c r="B30" s="181"/>
+      <c r="C30" s="185"/>
+      <c r="D30" s="186"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="186"/>
+      <c r="G30" s="186"/>
+      <c r="H30" s="187"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="186"/>
+      <c r="K30" s="186"/>
+      <c r="L30" s="187"/>
+      <c r="M30" s="185"/>
+      <c r="N30" s="186"/>
+      <c r="O30" s="186"/>
+      <c r="P30" s="187"/>
+      <c r="Q30" s="191"/>
+      <c r="R30" s="192"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="193"/>
+      <c r="U30" s="197"/>
+      <c r="V30" s="198"/>
+      <c r="W30" s="199"/>
+      <c r="X30" s="203"/>
+      <c r="Y30" s="204"/>
+      <c r="Z30" s="204"/>
+      <c r="AA30" s="205"/>
+      <c r="AB30" s="185"/>
+      <c r="AC30" s="186"/>
+      <c r="AD30" s="186"/>
+      <c r="AE30" s="187"/>
+      <c r="AF30" s="235"/>
       <c r="AG30" s="119"/>
       <c r="AH30" s="119"/>
     </row>
     <row r="31" spans="1:36" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="118"/>
-      <c r="B31" s="150">
+      <c r="B31" s="180">
         <v>4</v>
       </c>
-      <c r="C31" s="152"/>
-      <c r="D31" s="153"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="153"/>
-      <c r="G31" s="153"/>
-      <c r="H31" s="154"/>
-      <c r="I31" s="152"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="153"/>
-      <c r="L31" s="154"/>
-      <c r="M31" s="237"/>
-      <c r="N31" s="238"/>
-      <c r="O31" s="238"/>
-      <c r="P31" s="239"/>
-      <c r="Q31" s="158"/>
-      <c r="R31" s="159"/>
-      <c r="S31" s="159"/>
-      <c r="T31" s="160"/>
-      <c r="U31" s="164"/>
-      <c r="V31" s="165"/>
-      <c r="W31" s="166"/>
-      <c r="X31" s="170"/>
-      <c r="Y31" s="171"/>
-      <c r="Z31" s="171"/>
-      <c r="AA31" s="172"/>
-      <c r="AB31" s="152"/>
-      <c r="AC31" s="153"/>
-      <c r="AD31" s="153"/>
-      <c r="AE31" s="154"/>
-      <c r="AF31" s="229" t="s">
-        <v>5</v>
+      <c r="C31" s="182"/>
+      <c r="D31" s="183"/>
+      <c r="E31" s="183"/>
+      <c r="F31" s="183"/>
+      <c r="G31" s="183"/>
+      <c r="H31" s="184"/>
+      <c r="I31" s="182"/>
+      <c r="J31" s="183"/>
+      <c r="K31" s="183"/>
+      <c r="L31" s="184"/>
+      <c r="M31" s="182"/>
+      <c r="N31" s="183"/>
+      <c r="O31" s="183"/>
+      <c r="P31" s="184"/>
+      <c r="Q31" s="188"/>
+      <c r="R31" s="189"/>
+      <c r="S31" s="189"/>
+      <c r="T31" s="190"/>
+      <c r="U31" s="194"/>
+      <c r="V31" s="195"/>
+      <c r="W31" s="196"/>
+      <c r="X31" s="200"/>
+      <c r="Y31" s="201"/>
+      <c r="Z31" s="201"/>
+      <c r="AA31" s="202"/>
+      <c r="AB31" s="182"/>
+      <c r="AC31" s="183"/>
+      <c r="AD31" s="183"/>
+      <c r="AE31" s="184"/>
+      <c r="AF31" s="234" t="s">
+        <v>6</v>
       </c>
       <c r="AG31" s="119"/>
       <c r="AH31" s="119"/>
     </row>
     <row r="32" spans="1:36" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="118"/>
-      <c r="B32" s="151"/>
-      <c r="C32" s="155"/>
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="156"/>
-      <c r="G32" s="156"/>
-      <c r="H32" s="157"/>
-      <c r="I32" s="155"/>
-      <c r="J32" s="156"/>
-      <c r="K32" s="156"/>
-      <c r="L32" s="157"/>
-      <c r="M32" s="240"/>
-      <c r="N32" s="241"/>
-      <c r="O32" s="241"/>
-      <c r="P32" s="242"/>
-      <c r="Q32" s="161"/>
-      <c r="R32" s="162"/>
-      <c r="S32" s="162"/>
-      <c r="T32" s="163"/>
-      <c r="U32" s="167"/>
-      <c r="V32" s="168"/>
-      <c r="W32" s="169"/>
-      <c r="X32" s="173"/>
-      <c r="Y32" s="174"/>
-      <c r="Z32" s="174"/>
-      <c r="AA32" s="175"/>
-      <c r="AB32" s="155"/>
-      <c r="AC32" s="156"/>
-      <c r="AD32" s="156"/>
-      <c r="AE32" s="157"/>
-      <c r="AF32" s="230"/>
+      <c r="B32" s="181"/>
+      <c r="C32" s="185"/>
+      <c r="D32" s="186"/>
+      <c r="E32" s="186"/>
+      <c r="F32" s="186"/>
+      <c r="G32" s="186"/>
+      <c r="H32" s="187"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="186"/>
+      <c r="K32" s="186"/>
+      <c r="L32" s="187"/>
+      <c r="M32" s="185"/>
+      <c r="N32" s="186"/>
+      <c r="O32" s="186"/>
+      <c r="P32" s="187"/>
+      <c r="Q32" s="191"/>
+      <c r="R32" s="192"/>
+      <c r="S32" s="192"/>
+      <c r="T32" s="193"/>
+      <c r="U32" s="197"/>
+      <c r="V32" s="198"/>
+      <c r="W32" s="199"/>
+      <c r="X32" s="203"/>
+      <c r="Y32" s="204"/>
+      <c r="Z32" s="204"/>
+      <c r="AA32" s="205"/>
+      <c r="AB32" s="185"/>
+      <c r="AC32" s="186"/>
+      <c r="AD32" s="186"/>
+      <c r="AE32" s="187"/>
+      <c r="AF32" s="235"/>
       <c r="AG32" s="119"/>
       <c r="AH32" s="119"/>
     </row>
     <row r="33" spans="1:34" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="118"/>
-      <c r="B33" s="150">
+      <c r="B33" s="180">
         <v>5</v>
       </c>
-      <c r="C33" s="152"/>
-      <c r="D33" s="153"/>
-      <c r="E33" s="153"/>
-      <c r="F33" s="153"/>
-      <c r="G33" s="153"/>
-      <c r="H33" s="154"/>
-      <c r="I33" s="152"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="154"/>
-      <c r="M33" s="237"/>
-      <c r="N33" s="238"/>
-      <c r="O33" s="238"/>
-      <c r="P33" s="239"/>
-      <c r="Q33" s="158"/>
-      <c r="R33" s="159"/>
-      <c r="S33" s="159"/>
-      <c r="T33" s="160"/>
-      <c r="U33" s="164"/>
-      <c r="V33" s="165"/>
-      <c r="W33" s="166"/>
-      <c r="X33" s="170"/>
-      <c r="Y33" s="171"/>
-      <c r="Z33" s="171"/>
-      <c r="AA33" s="172"/>
-      <c r="AB33" s="152"/>
-      <c r="AC33" s="153"/>
-      <c r="AD33" s="153"/>
-      <c r="AE33" s="154"/>
-      <c r="AF33" s="229" t="s">
-        <v>5</v>
+      <c r="C33" s="182"/>
+      <c r="D33" s="183"/>
+      <c r="E33" s="183"/>
+      <c r="F33" s="183"/>
+      <c r="G33" s="183"/>
+      <c r="H33" s="184"/>
+      <c r="I33" s="182"/>
+      <c r="J33" s="183"/>
+      <c r="K33" s="183"/>
+      <c r="L33" s="184"/>
+      <c r="M33" s="182"/>
+      <c r="N33" s="183"/>
+      <c r="O33" s="183"/>
+      <c r="P33" s="184"/>
+      <c r="Q33" s="188"/>
+      <c r="R33" s="189"/>
+      <c r="S33" s="189"/>
+      <c r="T33" s="190"/>
+      <c r="U33" s="194"/>
+      <c r="V33" s="195"/>
+      <c r="W33" s="196"/>
+      <c r="X33" s="200"/>
+      <c r="Y33" s="201"/>
+      <c r="Z33" s="201"/>
+      <c r="AA33" s="202"/>
+      <c r="AB33" s="182"/>
+      <c r="AC33" s="183"/>
+      <c r="AD33" s="183"/>
+      <c r="AE33" s="184"/>
+      <c r="AF33" s="234" t="s">
+        <v>6</v>
       </c>
       <c r="AG33" s="119"/>
       <c r="AH33" s="119"/>
     </row>
     <row r="34" spans="1:34" s="96" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="118"/>
-      <c r="B34" s="151"/>
-      <c r="C34" s="155"/>
-      <c r="D34" s="156"/>
-      <c r="E34" s="156"/>
-      <c r="F34" s="156"/>
-      <c r="G34" s="156"/>
-      <c r="H34" s="157"/>
-      <c r="I34" s="155"/>
-      <c r="J34" s="156"/>
-      <c r="K34" s="156"/>
-      <c r="L34" s="157"/>
-      <c r="M34" s="240"/>
-      <c r="N34" s="241"/>
-      <c r="O34" s="241"/>
-      <c r="P34" s="242"/>
-      <c r="Q34" s="161"/>
-      <c r="R34" s="162"/>
-      <c r="S34" s="162"/>
-      <c r="T34" s="163"/>
-      <c r="U34" s="167"/>
-      <c r="V34" s="168"/>
-      <c r="W34" s="169"/>
-      <c r="X34" s="173"/>
-      <c r="Y34" s="174"/>
-      <c r="Z34" s="174"/>
-      <c r="AA34" s="175"/>
-      <c r="AB34" s="155"/>
-      <c r="AC34" s="156"/>
-      <c r="AD34" s="156"/>
-      <c r="AE34" s="157"/>
-      <c r="AF34" s="230"/>
+      <c r="B34" s="181"/>
+      <c r="C34" s="185"/>
+      <c r="D34" s="186"/>
+      <c r="E34" s="186"/>
+      <c r="F34" s="186"/>
+      <c r="G34" s="186"/>
+      <c r="H34" s="187"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="186"/>
+      <c r="K34" s="186"/>
+      <c r="L34" s="187"/>
+      <c r="M34" s="185"/>
+      <c r="N34" s="186"/>
+      <c r="O34" s="186"/>
+      <c r="P34" s="187"/>
+      <c r="Q34" s="191"/>
+      <c r="R34" s="192"/>
+      <c r="S34" s="192"/>
+      <c r="T34" s="193"/>
+      <c r="U34" s="197"/>
+      <c r="V34" s="198"/>
+      <c r="W34" s="199"/>
+      <c r="X34" s="203"/>
+      <c r="Y34" s="204"/>
+      <c r="Z34" s="204"/>
+      <c r="AA34" s="205"/>
+      <c r="AB34" s="185"/>
+      <c r="AC34" s="186"/>
+      <c r="AD34" s="186"/>
+      <c r="AE34" s="187"/>
+      <c r="AF34" s="235"/>
       <c r="AG34" s="119"/>
       <c r="AH34" s="119"/>
     </row>
     <row r="35" spans="1:34" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="118"/>
       <c r="B35" s="44"/>
-      <c r="C35" s="234" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" s="235"/>
-      <c r="E35" s="235"/>
-      <c r="F35" s="235"/>
-      <c r="G35" s="235"/>
-      <c r="H35" s="235"/>
-      <c r="I35" s="235"/>
-      <c r="J35" s="235"/>
-      <c r="K35" s="235"/>
-      <c r="L35" s="235"/>
-      <c r="M35" s="235"/>
-      <c r="N35" s="235"/>
-      <c r="O35" s="235"/>
-      <c r="P35" s="235"/>
-      <c r="Q35" s="235"/>
-      <c r="R35" s="235"/>
-      <c r="S35" s="235"/>
-      <c r="T35" s="235"/>
-      <c r="U35" s="235"/>
-      <c r="V35" s="235"/>
-      <c r="W35" s="236"/>
-      <c r="X35" s="188"/>
-      <c r="Y35" s="189"/>
-      <c r="Z35" s="189"/>
-      <c r="AA35" s="190"/>
-      <c r="AB35" s="185"/>
-      <c r="AC35" s="186"/>
-      <c r="AD35" s="186"/>
-      <c r="AE35" s="187"/>
+      <c r="C35" s="258" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="259"/>
+      <c r="E35" s="259"/>
+      <c r="F35" s="259"/>
+      <c r="G35" s="259"/>
+      <c r="H35" s="259"/>
+      <c r="I35" s="259"/>
+      <c r="J35" s="259"/>
+      <c r="K35" s="259"/>
+      <c r="L35" s="259"/>
+      <c r="M35" s="259"/>
+      <c r="N35" s="259"/>
+      <c r="O35" s="259"/>
+      <c r="P35" s="259"/>
+      <c r="Q35" s="259"/>
+      <c r="R35" s="259"/>
+      <c r="S35" s="259"/>
+      <c r="T35" s="259"/>
+      <c r="U35" s="259"/>
+      <c r="V35" s="259"/>
+      <c r="W35" s="260"/>
+      <c r="X35" s="254"/>
+      <c r="Y35" s="230"/>
+      <c r="Z35" s="230"/>
+      <c r="AA35" s="231"/>
+      <c r="AB35" s="253"/>
+      <c r="AC35" s="239"/>
+      <c r="AD35" s="239"/>
+      <c r="AE35" s="244"/>
       <c r="AF35" s="41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG35" s="119"/>
       <c r="AH35" s="119"/>
@@ -7688,41 +7632,41 @@
     <row r="36" spans="1:34" s="96" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="118"/>
       <c r="B36" s="44"/>
-      <c r="C36" s="254" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="255"/>
-      <c r="E36" s="255"/>
-      <c r="F36" s="255"/>
-      <c r="G36" s="255"/>
-      <c r="H36" s="255"/>
-      <c r="I36" s="255"/>
-      <c r="J36" s="186"/>
-      <c r="K36" s="186"/>
-      <c r="L36" s="186"/>
-      <c r="M36" s="186"/>
-      <c r="N36" s="186"/>
-      <c r="O36" s="186"/>
-      <c r="P36" s="186"/>
-      <c r="Q36" s="186"/>
-      <c r="R36" s="186"/>
-      <c r="S36" s="186"/>
+      <c r="C36" s="251" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="252"/>
+      <c r="E36" s="252"/>
+      <c r="F36" s="252"/>
+      <c r="G36" s="252"/>
+      <c r="H36" s="252"/>
+      <c r="I36" s="252"/>
+      <c r="J36" s="239"/>
+      <c r="K36" s="239"/>
+      <c r="L36" s="239"/>
+      <c r="M36" s="239"/>
+      <c r="N36" s="239"/>
+      <c r="O36" s="239"/>
+      <c r="P36" s="239"/>
+      <c r="Q36" s="239"/>
+      <c r="R36" s="239"/>
+      <c r="S36" s="239"/>
       <c r="T36" s="120" t="s">
-        <v>45</v>
-      </c>
-      <c r="U36" s="250"/>
-      <c r="V36" s="183"/>
-      <c r="W36" s="184"/>
-      <c r="X36" s="199"/>
-      <c r="Y36" s="171"/>
-      <c r="Z36" s="171"/>
-      <c r="AA36" s="172"/>
-      <c r="AB36" s="185"/>
-      <c r="AC36" s="186"/>
-      <c r="AD36" s="186"/>
-      <c r="AE36" s="187"/>
+        <v>46</v>
+      </c>
+      <c r="U36" s="236"/>
+      <c r="V36" s="237"/>
+      <c r="W36" s="238"/>
+      <c r="X36" s="281"/>
+      <c r="Y36" s="201"/>
+      <c r="Z36" s="201"/>
+      <c r="AA36" s="202"/>
+      <c r="AB36" s="253"/>
+      <c r="AC36" s="239"/>
+      <c r="AD36" s="239"/>
+      <c r="AE36" s="244"/>
       <c r="AF36" s="41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG36" s="119"/>
       <c r="AH36" s="119"/>
@@ -7751,15 +7695,15 @@
       <c r="U37" s="40"/>
       <c r="V37" s="40"/>
       <c r="W37" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="X37" s="231">
+        <v>49</v>
+      </c>
+      <c r="X37" s="255">
         <f>SUM(X24:X36)</f>
         <v>0</v>
       </c>
-      <c r="Y37" s="232"/>
-      <c r="Z37" s="232"/>
-      <c r="AA37" s="233"/>
+      <c r="Y37" s="256"/>
+      <c r="Z37" s="256"/>
+      <c r="AA37" s="257"/>
       <c r="AB37" s="78"/>
       <c r="AC37" s="78"/>
       <c r="AD37" s="78"/>
@@ -7773,39 +7717,39 @@
       <c r="B38" s="44">
         <v>6</v>
       </c>
-      <c r="C38" s="185"/>
-      <c r="D38" s="186"/>
-      <c r="E38" s="186"/>
-      <c r="F38" s="186"/>
-      <c r="G38" s="186"/>
-      <c r="H38" s="187"/>
-      <c r="I38" s="185"/>
-      <c r="J38" s="186"/>
-      <c r="K38" s="186"/>
-      <c r="L38" s="187"/>
-      <c r="M38" s="176" t="s">
-        <v>46</v>
-      </c>
-      <c r="N38" s="177"/>
-      <c r="O38" s="177"/>
-      <c r="P38" s="178"/>
-      <c r="Q38" s="179"/>
-      <c r="R38" s="180"/>
-      <c r="S38" s="180"/>
-      <c r="T38" s="181"/>
-      <c r="U38" s="182"/>
-      <c r="V38" s="183"/>
-      <c r="W38" s="184"/>
-      <c r="X38" s="173"/>
-      <c r="Y38" s="174"/>
-      <c r="Z38" s="174"/>
-      <c r="AA38" s="175"/>
-      <c r="AB38" s="185"/>
-      <c r="AC38" s="186"/>
-      <c r="AD38" s="186"/>
-      <c r="AE38" s="187"/>
+      <c r="C38" s="253"/>
+      <c r="D38" s="239"/>
+      <c r="E38" s="239"/>
+      <c r="F38" s="239"/>
+      <c r="G38" s="239"/>
+      <c r="H38" s="244"/>
+      <c r="I38" s="253"/>
+      <c r="J38" s="239"/>
+      <c r="K38" s="239"/>
+      <c r="L38" s="244"/>
+      <c r="M38" s="273" t="s">
+        <v>47</v>
+      </c>
+      <c r="N38" s="274"/>
+      <c r="O38" s="274"/>
+      <c r="P38" s="275"/>
+      <c r="Q38" s="276"/>
+      <c r="R38" s="277"/>
+      <c r="S38" s="277"/>
+      <c r="T38" s="278"/>
+      <c r="U38" s="279"/>
+      <c r="V38" s="237"/>
+      <c r="W38" s="238"/>
+      <c r="X38" s="203"/>
+      <c r="Y38" s="204"/>
+      <c r="Z38" s="204"/>
+      <c r="AA38" s="205"/>
+      <c r="AB38" s="253"/>
+      <c r="AC38" s="239"/>
+      <c r="AD38" s="239"/>
+      <c r="AE38" s="244"/>
       <c r="AF38" s="41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG38" s="119"/>
       <c r="AH38" s="119"/>
@@ -7815,39 +7759,39 @@
       <c r="B39" s="44">
         <v>7</v>
       </c>
-      <c r="C39" s="185"/>
-      <c r="D39" s="186"/>
-      <c r="E39" s="186"/>
-      <c r="F39" s="186"/>
-      <c r="G39" s="186"/>
-      <c r="H39" s="187"/>
-      <c r="I39" s="185"/>
-      <c r="J39" s="186"/>
-      <c r="K39" s="186"/>
-      <c r="L39" s="187"/>
-      <c r="M39" s="176" t="s">
-        <v>47</v>
-      </c>
-      <c r="N39" s="177"/>
-      <c r="O39" s="177"/>
-      <c r="P39" s="178"/>
-      <c r="Q39" s="179"/>
-      <c r="R39" s="180"/>
-      <c r="S39" s="180"/>
-      <c r="T39" s="181"/>
-      <c r="U39" s="182"/>
-      <c r="V39" s="183"/>
-      <c r="W39" s="184"/>
-      <c r="X39" s="188"/>
-      <c r="Y39" s="189"/>
-      <c r="Z39" s="189"/>
-      <c r="AA39" s="190"/>
-      <c r="AB39" s="185"/>
-      <c r="AC39" s="186"/>
-      <c r="AD39" s="186"/>
-      <c r="AE39" s="187"/>
+      <c r="C39" s="253"/>
+      <c r="D39" s="239"/>
+      <c r="E39" s="239"/>
+      <c r="F39" s="239"/>
+      <c r="G39" s="239"/>
+      <c r="H39" s="244"/>
+      <c r="I39" s="253"/>
+      <c r="J39" s="239"/>
+      <c r="K39" s="239"/>
+      <c r="L39" s="244"/>
+      <c r="M39" s="273" t="s">
+        <v>48</v>
+      </c>
+      <c r="N39" s="274"/>
+      <c r="O39" s="274"/>
+      <c r="P39" s="275"/>
+      <c r="Q39" s="276"/>
+      <c r="R39" s="277"/>
+      <c r="S39" s="277"/>
+      <c r="T39" s="278"/>
+      <c r="U39" s="279"/>
+      <c r="V39" s="237"/>
+      <c r="W39" s="238"/>
+      <c r="X39" s="254"/>
+      <c r="Y39" s="230"/>
+      <c r="Z39" s="230"/>
+      <c r="AA39" s="231"/>
+      <c r="AB39" s="253"/>
+      <c r="AC39" s="239"/>
+      <c r="AD39" s="239"/>
+      <c r="AE39" s="244"/>
       <c r="AF39" s="41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG39" s="119"/>
       <c r="AH39" s="119"/>
@@ -7876,15 +7820,15 @@
       <c r="U40" s="123"/>
       <c r="V40" s="123"/>
       <c r="W40" s="124" t="s">
-        <v>49</v>
-      </c>
-      <c r="X40" s="251">
+        <v>50</v>
+      </c>
+      <c r="X40" s="245">
         <f>SUM(X38:X39)</f>
         <v>0</v>
       </c>
-      <c r="Y40" s="252"/>
-      <c r="Z40" s="252"/>
-      <c r="AA40" s="253"/>
+      <c r="Y40" s="246"/>
+      <c r="Z40" s="246"/>
+      <c r="AA40" s="247"/>
       <c r="AB40" s="125"/>
       <c r="AC40" s="125"/>
       <c r="AD40" s="125"/>
@@ -7895,37 +7839,37 @@
     </row>
     <row r="41" spans="1:34" s="31" customFormat="1" ht="32.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="32"/>
-      <c r="B41" s="211" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" s="212"/>
-      <c r="D41" s="212"/>
-      <c r="E41" s="212"/>
-      <c r="F41" s="212"/>
-      <c r="G41" s="212"/>
-      <c r="H41" s="212"/>
-      <c r="I41" s="212"/>
-      <c r="J41" s="212"/>
-      <c r="K41" s="212"/>
-      <c r="L41" s="212"/>
-      <c r="M41" s="212"/>
-      <c r="N41" s="212"/>
-      <c r="O41" s="212"/>
-      <c r="P41" s="212"/>
-      <c r="Q41" s="212"/>
-      <c r="R41" s="212"/>
-      <c r="S41" s="212"/>
-      <c r="T41" s="212"/>
-      <c r="U41" s="212"/>
-      <c r="V41" s="212"/>
-      <c r="W41" s="213"/>
-      <c r="X41" s="147">
+      <c r="B41" s="160" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="267"/>
+      <c r="D41" s="267"/>
+      <c r="E41" s="267"/>
+      <c r="F41" s="267"/>
+      <c r="G41" s="267"/>
+      <c r="H41" s="267"/>
+      <c r="I41" s="267"/>
+      <c r="J41" s="267"/>
+      <c r="K41" s="267"/>
+      <c r="L41" s="267"/>
+      <c r="M41" s="267"/>
+      <c r="N41" s="267"/>
+      <c r="O41" s="267"/>
+      <c r="P41" s="267"/>
+      <c r="Q41" s="267"/>
+      <c r="R41" s="267"/>
+      <c r="S41" s="267"/>
+      <c r="T41" s="267"/>
+      <c r="U41" s="267"/>
+      <c r="V41" s="267"/>
+      <c r="W41" s="268"/>
+      <c r="X41" s="248">
         <f>X37+X40</f>
         <v>0</v>
       </c>
-      <c r="Y41" s="148"/>
-      <c r="Z41" s="148"/>
-      <c r="AA41" s="149"/>
+      <c r="Y41" s="249"/>
+      <c r="Z41" s="249"/>
+      <c r="AA41" s="250"/>
       <c r="AB41" s="98"/>
       <c r="AC41" s="98"/>
       <c r="AD41" s="98"/>
@@ -7972,60 +7916,60 @@
     </row>
     <row r="43" spans="1:34" s="31" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="32"/>
-      <c r="B43" s="220" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="221"/>
-      <c r="D43" s="221"/>
-      <c r="E43" s="221"/>
-      <c r="F43" s="221"/>
-      <c r="G43" s="221"/>
-      <c r="H43" s="221"/>
-      <c r="I43" s="221"/>
-      <c r="J43" s="221"/>
-      <c r="K43" s="221"/>
-      <c r="L43" s="221"/>
-      <c r="M43" s="221"/>
-      <c r="N43" s="221"/>
-      <c r="O43" s="221"/>
-      <c r="P43" s="221"/>
-      <c r="Q43" s="221"/>
-      <c r="R43" s="221"/>
-      <c r="S43" s="221"/>
-      <c r="T43" s="221"/>
-      <c r="U43" s="221"/>
-      <c r="V43" s="221"/>
-      <c r="W43" s="221"/>
-      <c r="X43" s="221"/>
-      <c r="Y43" s="221"/>
-      <c r="Z43" s="221"/>
-      <c r="AA43" s="221"/>
-      <c r="AB43" s="221"/>
-      <c r="AC43" s="221"/>
-      <c r="AD43" s="221"/>
-      <c r="AE43" s="221"/>
-      <c r="AF43" s="221"/>
+      <c r="B43" s="269" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="150"/>
+      <c r="D43" s="150"/>
+      <c r="E43" s="150"/>
+      <c r="F43" s="150"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="150"/>
+      <c r="I43" s="150"/>
+      <c r="J43" s="150"/>
+      <c r="K43" s="150"/>
+      <c r="L43" s="150"/>
+      <c r="M43" s="150"/>
+      <c r="N43" s="150"/>
+      <c r="O43" s="150"/>
+      <c r="P43" s="150"/>
+      <c r="Q43" s="150"/>
+      <c r="R43" s="150"/>
+      <c r="S43" s="150"/>
+      <c r="T43" s="150"/>
+      <c r="U43" s="150"/>
+      <c r="V43" s="150"/>
+      <c r="W43" s="150"/>
+      <c r="X43" s="150"/>
+      <c r="Y43" s="150"/>
+      <c r="Z43" s="150"/>
+      <c r="AA43" s="150"/>
+      <c r="AB43" s="150"/>
+      <c r="AC43" s="150"/>
+      <c r="AD43" s="150"/>
+      <c r="AE43" s="150"/>
+      <c r="AF43" s="150"/>
       <c r="AG43" s="30"/>
       <c r="AH43" s="30"/>
     </row>
     <row r="44" spans="1:34" s="31" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="32"/>
-      <c r="B44" s="217" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="218"/>
+      <c r="B44" s="169" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="170"/>
       <c r="D44" s="35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E44" s="35"/>
       <c r="F44" s="35"/>
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
       <c r="I44" s="141" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J44" s="35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
@@ -8034,10 +7978,10 @@
       <c r="O44" s="35"/>
       <c r="P44" s="35"/>
       <c r="Q44" s="141" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R44" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S44" s="100"/>
       <c r="T44" s="23"/>
@@ -8095,49 +8039,49 @@
     <row r="46" spans="1:34" s="31" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="32"/>
       <c r="B46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="193" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="205"/>
-      <c r="E46" s="205"/>
-      <c r="F46" s="205"/>
-      <c r="G46" s="206"/>
-      <c r="H46" s="202" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" s="166" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="264"/>
+      <c r="E46" s="264"/>
+      <c r="F46" s="264"/>
+      <c r="G46" s="265"/>
+      <c r="H46" s="261" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" s="264"/>
+      <c r="J46" s="264"/>
+      <c r="K46" s="264"/>
+      <c r="L46" s="264"/>
+      <c r="M46" s="264"/>
+      <c r="N46" s="264"/>
+      <c r="O46" s="264"/>
+      <c r="P46" s="264"/>
+      <c r="Q46" s="264"/>
+      <c r="R46" s="265"/>
+      <c r="S46" s="261" t="s">
+        <v>57</v>
+      </c>
+      <c r="T46" s="262"/>
+      <c r="U46" s="262"/>
+      <c r="V46" s="262"/>
+      <c r="W46" s="263"/>
+      <c r="X46" s="166" t="s">
         <v>55</v>
       </c>
-      <c r="I46" s="205"/>
-      <c r="J46" s="205"/>
-      <c r="K46" s="205"/>
-      <c r="L46" s="205"/>
-      <c r="M46" s="205"/>
-      <c r="N46" s="205"/>
-      <c r="O46" s="205"/>
-      <c r="P46" s="205"/>
-      <c r="Q46" s="205"/>
-      <c r="R46" s="206"/>
-      <c r="S46" s="202" t="s">
-        <v>56</v>
-      </c>
-      <c r="T46" s="203"/>
-      <c r="U46" s="203"/>
-      <c r="V46" s="203"/>
-      <c r="W46" s="204"/>
-      <c r="X46" s="193" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y46" s="194"/>
-      <c r="Z46" s="194"/>
-      <c r="AA46" s="195"/>
-      <c r="AB46" s="193" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC46" s="194"/>
-      <c r="AD46" s="194"/>
-      <c r="AE46" s="195"/>
+      <c r="Y46" s="167"/>
+      <c r="Z46" s="167"/>
+      <c r="AA46" s="168"/>
+      <c r="AB46" s="166" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC46" s="167"/>
+      <c r="AD46" s="167"/>
+      <c r="AE46" s="168"/>
       <c r="AF46" s="37" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG46" s="30"/>
       <c r="AH46" s="30"/>
@@ -8147,37 +8091,37 @@
       <c r="B47" s="51">
         <v>1</v>
       </c>
-      <c r="C47" s="219"/>
-      <c r="D47" s="209"/>
-      <c r="E47" s="209"/>
-      <c r="F47" s="209"/>
-      <c r="G47" s="210"/>
-      <c r="H47" s="208"/>
-      <c r="I47" s="209"/>
-      <c r="J47" s="209"/>
-      <c r="K47" s="209"/>
-      <c r="L47" s="209"/>
-      <c r="M47" s="209"/>
-      <c r="N47" s="209"/>
-      <c r="O47" s="209"/>
-      <c r="P47" s="209"/>
-      <c r="Q47" s="209"/>
-      <c r="R47" s="210"/>
-      <c r="S47" s="225"/>
-      <c r="T47" s="226"/>
-      <c r="U47" s="226"/>
-      <c r="V47" s="226"/>
-      <c r="W47" s="227"/>
-      <c r="X47" s="222"/>
-      <c r="Y47" s="223"/>
-      <c r="Z47" s="223"/>
-      <c r="AA47" s="224"/>
-      <c r="AB47" s="219"/>
-      <c r="AC47" s="209"/>
-      <c r="AD47" s="209"/>
-      <c r="AE47" s="210"/>
+      <c r="C47" s="240"/>
+      <c r="D47" s="241"/>
+      <c r="E47" s="241"/>
+      <c r="F47" s="241"/>
+      <c r="G47" s="242"/>
+      <c r="H47" s="266"/>
+      <c r="I47" s="241"/>
+      <c r="J47" s="241"/>
+      <c r="K47" s="241"/>
+      <c r="L47" s="241"/>
+      <c r="M47" s="241"/>
+      <c r="N47" s="241"/>
+      <c r="O47" s="241"/>
+      <c r="P47" s="241"/>
+      <c r="Q47" s="241"/>
+      <c r="R47" s="242"/>
+      <c r="S47" s="400"/>
+      <c r="T47" s="401"/>
+      <c r="U47" s="402"/>
+      <c r="V47" s="400"/>
+      <c r="W47" s="402"/>
+      <c r="X47" s="270"/>
+      <c r="Y47" s="271"/>
+      <c r="Z47" s="271"/>
+      <c r="AA47" s="272"/>
+      <c r="AB47" s="240"/>
+      <c r="AC47" s="241"/>
+      <c r="AD47" s="241"/>
+      <c r="AE47" s="242"/>
       <c r="AF47" s="52" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG47" s="142"/>
       <c r="AH47" s="119"/>
@@ -8187,37 +8131,37 @@
       <c r="B48" s="44">
         <v>2</v>
       </c>
-      <c r="C48" s="207"/>
-      <c r="D48" s="186"/>
-      <c r="E48" s="186"/>
-      <c r="F48" s="186"/>
-      <c r="G48" s="187"/>
-      <c r="H48" s="185"/>
-      <c r="I48" s="186"/>
-      <c r="J48" s="186"/>
-      <c r="K48" s="186"/>
-      <c r="L48" s="186"/>
-      <c r="M48" s="186"/>
-      <c r="N48" s="186"/>
-      <c r="O48" s="186"/>
-      <c r="P48" s="186"/>
-      <c r="Q48" s="186"/>
-      <c r="R48" s="187"/>
-      <c r="S48" s="214"/>
-      <c r="T48" s="215"/>
-      <c r="U48" s="215"/>
-      <c r="V48" s="215"/>
-      <c r="W48" s="216"/>
-      <c r="X48" s="228"/>
-      <c r="Y48" s="189"/>
-      <c r="Z48" s="189"/>
-      <c r="AA48" s="190"/>
-      <c r="AB48" s="207"/>
-      <c r="AC48" s="186"/>
-      <c r="AD48" s="186"/>
-      <c r="AE48" s="187"/>
+      <c r="C48" s="243"/>
+      <c r="D48" s="239"/>
+      <c r="E48" s="239"/>
+      <c r="F48" s="239"/>
+      <c r="G48" s="244"/>
+      <c r="H48" s="253"/>
+      <c r="I48" s="239"/>
+      <c r="J48" s="239"/>
+      <c r="K48" s="239"/>
+      <c r="L48" s="239"/>
+      <c r="M48" s="239"/>
+      <c r="N48" s="239"/>
+      <c r="O48" s="239"/>
+      <c r="P48" s="239"/>
+      <c r="Q48" s="239"/>
+      <c r="R48" s="244"/>
+      <c r="S48" s="405"/>
+      <c r="T48" s="403"/>
+      <c r="U48" s="404"/>
+      <c r="V48" s="403"/>
+      <c r="W48" s="404"/>
+      <c r="X48" s="229"/>
+      <c r="Y48" s="230"/>
+      <c r="Z48" s="230"/>
+      <c r="AA48" s="231"/>
+      <c r="AB48" s="243"/>
+      <c r="AC48" s="239"/>
+      <c r="AD48" s="239"/>
+      <c r="AE48" s="244"/>
       <c r="AF48" s="41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG48" s="142"/>
       <c r="AH48" s="119"/>
@@ -8227,37 +8171,37 @@
       <c r="B49" s="44">
         <v>3</v>
       </c>
-      <c r="C49" s="207"/>
-      <c r="D49" s="186"/>
-      <c r="E49" s="186"/>
-      <c r="F49" s="186"/>
-      <c r="G49" s="187"/>
-      <c r="H49" s="185"/>
-      <c r="I49" s="186"/>
-      <c r="J49" s="186"/>
-      <c r="K49" s="186"/>
-      <c r="L49" s="186"/>
-      <c r="M49" s="186"/>
-      <c r="N49" s="186"/>
-      <c r="O49" s="186"/>
-      <c r="P49" s="186"/>
-      <c r="Q49" s="186"/>
-      <c r="R49" s="187"/>
-      <c r="S49" s="214"/>
-      <c r="T49" s="215"/>
-      <c r="U49" s="215"/>
-      <c r="V49" s="215"/>
-      <c r="W49" s="216"/>
-      <c r="X49" s="228"/>
-      <c r="Y49" s="189"/>
-      <c r="Z49" s="189"/>
-      <c r="AA49" s="190"/>
-      <c r="AB49" s="207"/>
-      <c r="AC49" s="186"/>
-      <c r="AD49" s="186"/>
-      <c r="AE49" s="187"/>
+      <c r="C49" s="243"/>
+      <c r="D49" s="239"/>
+      <c r="E49" s="239"/>
+      <c r="F49" s="239"/>
+      <c r="G49" s="244"/>
+      <c r="H49" s="253"/>
+      <c r="I49" s="239"/>
+      <c r="J49" s="239"/>
+      <c r="K49" s="239"/>
+      <c r="L49" s="239"/>
+      <c r="M49" s="239"/>
+      <c r="N49" s="239"/>
+      <c r="O49" s="239"/>
+      <c r="P49" s="239"/>
+      <c r="Q49" s="239"/>
+      <c r="R49" s="244"/>
+      <c r="S49" s="405"/>
+      <c r="T49" s="403"/>
+      <c r="U49" s="404"/>
+      <c r="V49" s="403"/>
+      <c r="W49" s="404"/>
+      <c r="X49" s="229"/>
+      <c r="Y49" s="230"/>
+      <c r="Z49" s="230"/>
+      <c r="AA49" s="231"/>
+      <c r="AB49" s="243"/>
+      <c r="AC49" s="239"/>
+      <c r="AD49" s="239"/>
+      <c r="AE49" s="244"/>
       <c r="AF49" s="41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG49" s="142"/>
       <c r="AH49" s="119"/>
@@ -8267,37 +8211,37 @@
       <c r="B50" s="44">
         <v>4</v>
       </c>
-      <c r="C50" s="207"/>
-      <c r="D50" s="186"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="186"/>
-      <c r="G50" s="187"/>
-      <c r="H50" s="185"/>
-      <c r="I50" s="186"/>
-      <c r="J50" s="186"/>
-      <c r="K50" s="186"/>
-      <c r="L50" s="186"/>
-      <c r="M50" s="186"/>
-      <c r="N50" s="186"/>
-      <c r="O50" s="186"/>
-      <c r="P50" s="186"/>
-      <c r="Q50" s="186"/>
-      <c r="R50" s="187"/>
-      <c r="S50" s="214"/>
-      <c r="T50" s="215"/>
-      <c r="U50" s="215"/>
-      <c r="V50" s="215"/>
-      <c r="W50" s="216"/>
-      <c r="X50" s="228"/>
-      <c r="Y50" s="189"/>
-      <c r="Z50" s="189"/>
-      <c r="AA50" s="190"/>
-      <c r="AB50" s="207"/>
-      <c r="AC50" s="186"/>
-      <c r="AD50" s="186"/>
-      <c r="AE50" s="187"/>
+      <c r="C50" s="243"/>
+      <c r="D50" s="239"/>
+      <c r="E50" s="239"/>
+      <c r="F50" s="239"/>
+      <c r="G50" s="244"/>
+      <c r="H50" s="253"/>
+      <c r="I50" s="239"/>
+      <c r="J50" s="239"/>
+      <c r="K50" s="239"/>
+      <c r="L50" s="239"/>
+      <c r="M50" s="239"/>
+      <c r="N50" s="239"/>
+      <c r="O50" s="239"/>
+      <c r="P50" s="239"/>
+      <c r="Q50" s="239"/>
+      <c r="R50" s="244"/>
+      <c r="S50" s="405"/>
+      <c r="T50" s="403"/>
+      <c r="U50" s="404"/>
+      <c r="V50" s="403"/>
+      <c r="W50" s="404"/>
+      <c r="X50" s="229"/>
+      <c r="Y50" s="230"/>
+      <c r="Z50" s="230"/>
+      <c r="AA50" s="231"/>
+      <c r="AB50" s="243"/>
+      <c r="AC50" s="239"/>
+      <c r="AD50" s="239"/>
+      <c r="AE50" s="244"/>
       <c r="AF50" s="41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG50" s="142"/>
       <c r="AH50" s="119"/>
@@ -8307,37 +8251,37 @@
       <c r="B51" s="97">
         <v>5</v>
       </c>
-      <c r="C51" s="200"/>
-      <c r="D51" s="192"/>
-      <c r="E51" s="192"/>
-      <c r="F51" s="192"/>
-      <c r="G51" s="201"/>
-      <c r="H51" s="191"/>
-      <c r="I51" s="192"/>
-      <c r="J51" s="192"/>
-      <c r="K51" s="192"/>
-      <c r="L51" s="192"/>
-      <c r="M51" s="192"/>
-      <c r="N51" s="192"/>
-      <c r="O51" s="192"/>
-      <c r="P51" s="192"/>
-      <c r="Q51" s="192"/>
+      <c r="C51" s="226"/>
+      <c r="D51" s="227"/>
+      <c r="E51" s="227"/>
+      <c r="F51" s="227"/>
+      <c r="G51" s="228"/>
+      <c r="H51" s="280"/>
+      <c r="I51" s="227"/>
+      <c r="J51" s="227"/>
+      <c r="K51" s="227"/>
+      <c r="L51" s="227"/>
+      <c r="M51" s="227"/>
+      <c r="N51" s="227"/>
+      <c r="O51" s="227"/>
+      <c r="P51" s="227"/>
+      <c r="Q51" s="227"/>
       <c r="R51" s="145"/>
-      <c r="S51" s="196"/>
-      <c r="T51" s="197"/>
-      <c r="U51" s="197"/>
-      <c r="V51" s="197"/>
-      <c r="W51" s="198"/>
-      <c r="X51" s="243"/>
-      <c r="Y51" s="244"/>
-      <c r="Z51" s="244"/>
-      <c r="AA51" s="245"/>
-      <c r="AB51" s="200"/>
-      <c r="AC51" s="192"/>
-      <c r="AD51" s="192"/>
-      <c r="AE51" s="201"/>
+      <c r="S51" s="405"/>
+      <c r="T51" s="403"/>
+      <c r="U51" s="404"/>
+      <c r="V51" s="403"/>
+      <c r="W51" s="404"/>
+      <c r="X51" s="223"/>
+      <c r="Y51" s="224"/>
+      <c r="Z51" s="224"/>
+      <c r="AA51" s="225"/>
+      <c r="AB51" s="226"/>
+      <c r="AC51" s="227"/>
+      <c r="AD51" s="227"/>
+      <c r="AE51" s="228"/>
       <c r="AF51" s="53" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG51" s="142"/>
       <c r="AH51" s="119"/>
@@ -8346,37 +8290,37 @@
     </row>
     <row r="52" spans="1:36" s="31" customFormat="1" ht="32.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="32"/>
-      <c r="B52" s="211" t="s">
-        <v>50</v>
-      </c>
-      <c r="C52" s="293"/>
-      <c r="D52" s="293"/>
-      <c r="E52" s="293"/>
-      <c r="F52" s="293"/>
-      <c r="G52" s="293"/>
-      <c r="H52" s="293"/>
-      <c r="I52" s="293"/>
-      <c r="J52" s="293"/>
-      <c r="K52" s="293"/>
-      <c r="L52" s="293"/>
-      <c r="M52" s="293"/>
-      <c r="N52" s="293"/>
-      <c r="O52" s="293"/>
-      <c r="P52" s="293"/>
-      <c r="Q52" s="293"/>
-      <c r="R52" s="293"/>
-      <c r="S52" s="293"/>
-      <c r="T52" s="293"/>
-      <c r="U52" s="293"/>
-      <c r="V52" s="293"/>
-      <c r="W52" s="294"/>
-      <c r="X52" s="147">
+      <c r="B52" s="160" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="161"/>
+      <c r="D52" s="161"/>
+      <c r="E52" s="161"/>
+      <c r="F52" s="161"/>
+      <c r="G52" s="161"/>
+      <c r="H52" s="161"/>
+      <c r="I52" s="161"/>
+      <c r="J52" s="161"/>
+      <c r="K52" s="161"/>
+      <c r="L52" s="161"/>
+      <c r="M52" s="161"/>
+      <c r="N52" s="161"/>
+      <c r="O52" s="161"/>
+      <c r="P52" s="161"/>
+      <c r="Q52" s="161"/>
+      <c r="R52" s="161"/>
+      <c r="S52" s="161"/>
+      <c r="T52" s="161"/>
+      <c r="U52" s="161"/>
+      <c r="V52" s="161"/>
+      <c r="W52" s="162"/>
+      <c r="X52" s="248">
         <f>SUM(X46:X51)</f>
         <v>0</v>
       </c>
-      <c r="Y52" s="148"/>
-      <c r="Z52" s="148"/>
-      <c r="AA52" s="149"/>
+      <c r="Y52" s="249"/>
+      <c r="Z52" s="249"/>
+      <c r="AA52" s="250"/>
       <c r="AB52" s="54"/>
       <c r="AC52" s="55"/>
       <c r="AD52" s="55"/>
@@ -8466,7 +8410,7 @@
     <row r="55" spans="1:36" s="31" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="33"/>
       <c r="B55" s="65" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C55" s="45"/>
       <c r="D55" s="45"/>
@@ -8505,39 +8449,39 @@
     </row>
     <row r="56" spans="1:36" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="33"/>
-      <c r="B56" s="297" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" s="221"/>
-      <c r="D56" s="221"/>
-      <c r="E56" s="221"/>
-      <c r="F56" s="221"/>
-      <c r="G56" s="221"/>
-      <c r="H56" s="221"/>
-      <c r="I56" s="221"/>
-      <c r="J56" s="221"/>
-      <c r="K56" s="221"/>
-      <c r="L56" s="221"/>
-      <c r="M56" s="221"/>
-      <c r="N56" s="221"/>
-      <c r="O56" s="221"/>
-      <c r="P56" s="221"/>
-      <c r="Q56" s="221"/>
-      <c r="R56" s="221"/>
-      <c r="S56" s="221"/>
-      <c r="T56" s="221"/>
-      <c r="U56" s="221"/>
-      <c r="V56" s="221"/>
-      <c r="W56" s="221"/>
-      <c r="X56" s="221"/>
-      <c r="Y56" s="221"/>
-      <c r="Z56" s="221"/>
-      <c r="AA56" s="221"/>
-      <c r="AB56" s="221"/>
-      <c r="AC56" s="221"/>
-      <c r="AD56" s="221"/>
-      <c r="AE56" s="221"/>
-      <c r="AF56" s="298"/>
+      <c r="B56" s="149" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="150"/>
+      <c r="D56" s="150"/>
+      <c r="E56" s="150"/>
+      <c r="F56" s="150"/>
+      <c r="G56" s="150"/>
+      <c r="H56" s="150"/>
+      <c r="I56" s="150"/>
+      <c r="J56" s="150"/>
+      <c r="K56" s="150"/>
+      <c r="L56" s="150"/>
+      <c r="M56" s="150"/>
+      <c r="N56" s="150"/>
+      <c r="O56" s="150"/>
+      <c r="P56" s="150"/>
+      <c r="Q56" s="150"/>
+      <c r="R56" s="150"/>
+      <c r="S56" s="150"/>
+      <c r="T56" s="150"/>
+      <c r="U56" s="150"/>
+      <c r="V56" s="150"/>
+      <c r="W56" s="150"/>
+      <c r="X56" s="150"/>
+      <c r="Y56" s="150"/>
+      <c r="Z56" s="150"/>
+      <c r="AA56" s="150"/>
+      <c r="AB56" s="150"/>
+      <c r="AC56" s="150"/>
+      <c r="AD56" s="150"/>
+      <c r="AE56" s="150"/>
+      <c r="AF56" s="151"/>
       <c r="AG56" s="45"/>
       <c r="AH56" s="30"/>
       <c r="AI56" s="30"/>
@@ -8583,39 +8527,39 @@
     </row>
     <row r="58" spans="1:36" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="33"/>
-      <c r="B58" s="299" t="s">
-        <v>85</v>
-      </c>
-      <c r="C58" s="300"/>
-      <c r="D58" s="300"/>
-      <c r="E58" s="300"/>
-      <c r="F58" s="300"/>
-      <c r="G58" s="300"/>
-      <c r="H58" s="300"/>
-      <c r="I58" s="300"/>
-      <c r="J58" s="300"/>
-      <c r="K58" s="300"/>
-      <c r="L58" s="300"/>
-      <c r="M58" s="300"/>
-      <c r="N58" s="300"/>
-      <c r="O58" s="300"/>
-      <c r="P58" s="300"/>
-      <c r="Q58" s="300"/>
-      <c r="R58" s="300"/>
-      <c r="S58" s="300"/>
-      <c r="T58" s="300"/>
-      <c r="U58" s="300"/>
-      <c r="V58" s="300"/>
-      <c r="W58" s="300"/>
-      <c r="X58" s="300"/>
-      <c r="Y58" s="300"/>
-      <c r="Z58" s="300"/>
-      <c r="AA58" s="300"/>
-      <c r="AB58" s="300"/>
-      <c r="AC58" s="300"/>
-      <c r="AD58" s="300"/>
-      <c r="AE58" s="300"/>
-      <c r="AF58" s="301"/>
+      <c r="B58" s="156" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" s="157"/>
+      <c r="D58" s="157"/>
+      <c r="E58" s="157"/>
+      <c r="F58" s="157"/>
+      <c r="G58" s="157"/>
+      <c r="H58" s="157"/>
+      <c r="I58" s="157"/>
+      <c r="J58" s="157"/>
+      <c r="K58" s="157"/>
+      <c r="L58" s="157"/>
+      <c r="M58" s="157"/>
+      <c r="N58" s="157"/>
+      <c r="O58" s="157"/>
+      <c r="P58" s="157"/>
+      <c r="Q58" s="157"/>
+      <c r="R58" s="157"/>
+      <c r="S58" s="157"/>
+      <c r="T58" s="157"/>
+      <c r="U58" s="157"/>
+      <c r="V58" s="157"/>
+      <c r="W58" s="157"/>
+      <c r="X58" s="157"/>
+      <c r="Y58" s="157"/>
+      <c r="Z58" s="157"/>
+      <c r="AA58" s="157"/>
+      <c r="AB58" s="157"/>
+      <c r="AC58" s="157"/>
+      <c r="AD58" s="157"/>
+      <c r="AE58" s="157"/>
+      <c r="AF58" s="158"/>
       <c r="AG58" s="45"/>
       <c r="AH58" s="30"/>
       <c r="AI58" s="30"/>
@@ -8638,7 +8582,7 @@
       <c r="N59" s="69"/>
       <c r="O59" s="70"/>
       <c r="P59" s="71" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="Q59" s="70"/>
       <c r="R59" s="113"/>
@@ -8707,33 +8651,33 @@
       <c r="E61" s="73"/>
       <c r="F61" s="73"/>
       <c r="G61" s="73"/>
-      <c r="H61" s="302" t="s">
-        <v>86</v>
-      </c>
-      <c r="I61" s="300"/>
-      <c r="J61" s="300"/>
-      <c r="K61" s="300"/>
-      <c r="L61" s="300"/>
-      <c r="M61" s="300"/>
-      <c r="N61" s="300"/>
-      <c r="O61" s="300"/>
-      <c r="P61" s="300"/>
-      <c r="Q61" s="300"/>
-      <c r="R61" s="300"/>
-      <c r="S61" s="300"/>
-      <c r="T61" s="300"/>
-      <c r="U61" s="300"/>
-      <c r="V61" s="300"/>
-      <c r="W61" s="300"/>
-      <c r="X61" s="300"/>
-      <c r="Y61" s="300"/>
-      <c r="Z61" s="300"/>
-      <c r="AA61" s="300"/>
-      <c r="AB61" s="300"/>
-      <c r="AC61" s="300"/>
-      <c r="AD61" s="300"/>
-      <c r="AE61" s="300"/>
-      <c r="AF61" s="301"/>
+      <c r="H61" s="159" t="s">
+        <v>76</v>
+      </c>
+      <c r="I61" s="157"/>
+      <c r="J61" s="157"/>
+      <c r="K61" s="157"/>
+      <c r="L61" s="157"/>
+      <c r="M61" s="157"/>
+      <c r="N61" s="157"/>
+      <c r="O61" s="157"/>
+      <c r="P61" s="157"/>
+      <c r="Q61" s="157"/>
+      <c r="R61" s="157"/>
+      <c r="S61" s="157"/>
+      <c r="T61" s="157"/>
+      <c r="U61" s="157"/>
+      <c r="V61" s="157"/>
+      <c r="W61" s="157"/>
+      <c r="X61" s="157"/>
+      <c r="Y61" s="157"/>
+      <c r="Z61" s="157"/>
+      <c r="AA61" s="157"/>
+      <c r="AB61" s="157"/>
+      <c r="AC61" s="157"/>
+      <c r="AD61" s="157"/>
+      <c r="AE61" s="157"/>
+      <c r="AF61" s="158"/>
       <c r="AG61" s="45"/>
       <c r="AH61" s="30"/>
       <c r="AI61" s="30"/>
@@ -8756,7 +8700,7 @@
       <c r="N62" s="69"/>
       <c r="O62" s="69"/>
       <c r="P62" s="72" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="Q62" s="70"/>
       <c r="R62" s="113"/>
@@ -8857,9 +8801,7 @@
     </row>
     <row r="65" spans="1:36" s="61" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
-      <c r="B65" s="66" t="s">
-        <v>59</v>
-      </c>
+      <c r="B65" s="66"/>
       <c r="C65" s="62"/>
       <c r="D65" s="62"/>
       <c r="E65" s="62"/>
@@ -8898,13 +8840,9 @@
     <row r="66" spans="1:36" s="6" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
       <c r="B66" s="4"/>
-      <c r="C66" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D66" s="292"/>
-      <c r="E66" s="111" t="s">
-        <v>60</v>
-      </c>
+      <c r="C66" s="154"/>
+      <c r="D66" s="155"/>
+      <c r="E66" s="111"/>
       <c r="F66" s="111"/>
       <c r="G66" s="111"/>
       <c r="H66" s="111"/>
@@ -8936,47 +8874,35 @@
     <row r="67" spans="1:36" s="6" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5"/>
       <c r="B67" s="4"/>
-      <c r="C67" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="292"/>
-      <c r="E67" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="F67" s="290"/>
-      <c r="G67" s="290"/>
-      <c r="H67" s="290"/>
-      <c r="I67" s="290"/>
-      <c r="J67" s="290"/>
-      <c r="K67" s="290"/>
-      <c r="L67" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="M67" s="292"/>
-      <c r="N67" s="111" t="s">
-        <v>67</v>
-      </c>
+      <c r="C67" s="154"/>
+      <c r="D67" s="155"/>
+      <c r="E67" s="152"/>
+      <c r="F67" s="153"/>
+      <c r="G67" s="153"/>
+      <c r="H67" s="153"/>
+      <c r="I67" s="153"/>
+      <c r="J67" s="153"/>
+      <c r="K67" s="153"/>
+      <c r="L67" s="154"/>
+      <c r="M67" s="155"/>
+      <c r="N67" s="111"/>
       <c r="O67" s="7"/>
       <c r="P67" s="7"/>
       <c r="Q67" s="111"/>
       <c r="S67" s="111"/>
-      <c r="T67" s="117" t="s">
-        <v>5</v>
-      </c>
-      <c r="U67" s="295" t="s">
-        <v>68</v>
-      </c>
-      <c r="V67" s="296"/>
-      <c r="W67" s="296"/>
-      <c r="X67" s="296"/>
-      <c r="Y67" s="296"/>
-      <c r="Z67" s="296"/>
-      <c r="AA67" s="296"/>
-      <c r="AB67" s="296"/>
-      <c r="AC67" s="296"/>
-      <c r="AD67" s="296"/>
-      <c r="AE67" s="296"/>
-      <c r="AF67" s="296"/>
+      <c r="T67" s="117"/>
+      <c r="U67" s="147"/>
+      <c r="V67" s="148"/>
+      <c r="W67" s="148"/>
+      <c r="X67" s="148"/>
+      <c r="Y67" s="148"/>
+      <c r="Z67" s="148"/>
+      <c r="AA67" s="148"/>
+      <c r="AB67" s="148"/>
+      <c r="AC67" s="148"/>
+      <c r="AD67" s="148"/>
+      <c r="AE67" s="148"/>
+      <c r="AF67" s="148"/>
       <c r="AG67" s="107"/>
     </row>
     <row r="68" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -9004,9 +8930,7 @@
       <c r="AF68" s="5"/>
     </row>
     <row r="69" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="67" t="s">
-        <v>61</v>
-      </c>
+      <c r="B69" s="67"/>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
@@ -9038,13 +8962,9 @@
     </row>
     <row r="70" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="4"/>
-      <c r="C70" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="292"/>
-      <c r="E70" s="111" t="s">
-        <v>60</v>
-      </c>
+      <c r="C70" s="154"/>
+      <c r="D70" s="155"/>
+      <c r="E70" s="111"/>
       <c r="F70" s="111"/>
       <c r="G70" s="111"/>
       <c r="H70" s="111"/>
@@ -9074,47 +8994,35 @@
     </row>
     <row r="71" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B71" s="4"/>
-      <c r="C71" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71" s="292"/>
-      <c r="E71" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="F71" s="290"/>
-      <c r="G71" s="290"/>
-      <c r="H71" s="290"/>
-      <c r="I71" s="290"/>
-      <c r="J71" s="290"/>
-      <c r="K71" s="290"/>
-      <c r="L71" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="M71" s="292"/>
-      <c r="N71" s="111" t="s">
-        <v>67</v>
-      </c>
+      <c r="C71" s="154"/>
+      <c r="D71" s="155"/>
+      <c r="E71" s="152"/>
+      <c r="F71" s="153"/>
+      <c r="G71" s="153"/>
+      <c r="H71" s="153"/>
+      <c r="I71" s="153"/>
+      <c r="J71" s="153"/>
+      <c r="K71" s="153"/>
+      <c r="L71" s="154"/>
+      <c r="M71" s="155"/>
+      <c r="N71" s="111"/>
       <c r="O71" s="7"/>
       <c r="P71" s="7"/>
       <c r="Q71" s="111"/>
       <c r="S71" s="111"/>
-      <c r="T71" s="117" t="s">
-        <v>5</v>
-      </c>
-      <c r="U71" s="295" t="s">
-        <v>68</v>
-      </c>
-      <c r="V71" s="296"/>
-      <c r="W71" s="296"/>
-      <c r="X71" s="296"/>
-      <c r="Y71" s="296"/>
-      <c r="Z71" s="296"/>
-      <c r="AA71" s="296"/>
-      <c r="AB71" s="296"/>
-      <c r="AC71" s="296"/>
-      <c r="AD71" s="296"/>
-      <c r="AE71" s="296"/>
-      <c r="AF71" s="296"/>
+      <c r="T71" s="117"/>
+      <c r="U71" s="147"/>
+      <c r="V71" s="148"/>
+      <c r="W71" s="148"/>
+      <c r="X71" s="148"/>
+      <c r="Y71" s="148"/>
+      <c r="Z71" s="148"/>
+      <c r="AA71" s="148"/>
+      <c r="AB71" s="148"/>
+      <c r="AC71" s="148"/>
+      <c r="AD71" s="148"/>
+      <c r="AE71" s="148"/>
+      <c r="AF71" s="148"/>
     </row>
     <row r="72" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="9"/>
@@ -9148,9 +9056,7 @@
       <c r="AF72" s="5"/>
     </row>
     <row r="73" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="67" t="s">
-        <v>62</v>
-      </c>
+      <c r="B73" s="67"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
@@ -9182,13 +9088,9 @@
     </row>
     <row r="74" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="4"/>
-      <c r="C74" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="292"/>
-      <c r="E74" s="111" t="s">
-        <v>60</v>
-      </c>
+      <c r="C74" s="154"/>
+      <c r="D74" s="155"/>
+      <c r="E74" s="111"/>
       <c r="F74" s="111"/>
       <c r="G74" s="111"/>
       <c r="H74" s="111"/>
@@ -9218,47 +9120,35 @@
     </row>
     <row r="75" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="4"/>
-      <c r="C75" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="292"/>
-      <c r="E75" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="F75" s="290"/>
-      <c r="G75" s="290"/>
-      <c r="H75" s="290"/>
-      <c r="I75" s="290"/>
-      <c r="J75" s="290"/>
-      <c r="K75" s="290"/>
-      <c r="L75" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="M75" s="292"/>
-      <c r="N75" s="111" t="s">
-        <v>67</v>
-      </c>
+      <c r="C75" s="154"/>
+      <c r="D75" s="155"/>
+      <c r="E75" s="152"/>
+      <c r="F75" s="153"/>
+      <c r="G75" s="153"/>
+      <c r="H75" s="153"/>
+      <c r="I75" s="153"/>
+      <c r="J75" s="153"/>
+      <c r="K75" s="153"/>
+      <c r="L75" s="154"/>
+      <c r="M75" s="155"/>
+      <c r="N75" s="111"/>
       <c r="O75" s="7"/>
       <c r="P75" s="7"/>
       <c r="Q75" s="111"/>
       <c r="S75" s="111"/>
-      <c r="T75" s="117" t="s">
-        <v>5</v>
-      </c>
-      <c r="U75" s="295" t="s">
-        <v>68</v>
-      </c>
-      <c r="V75" s="296"/>
-      <c r="W75" s="296"/>
-      <c r="X75" s="296"/>
-      <c r="Y75" s="296"/>
-      <c r="Z75" s="296"/>
-      <c r="AA75" s="296"/>
-      <c r="AB75" s="296"/>
-      <c r="AC75" s="296"/>
-      <c r="AD75" s="296"/>
-      <c r="AE75" s="296"/>
-      <c r="AF75" s="296"/>
+      <c r="T75" s="117"/>
+      <c r="U75" s="147"/>
+      <c r="V75" s="148"/>
+      <c r="W75" s="148"/>
+      <c r="X75" s="148"/>
+      <c r="Y75" s="148"/>
+      <c r="Z75" s="148"/>
+      <c r="AA75" s="148"/>
+      <c r="AB75" s="148"/>
+      <c r="AC75" s="148"/>
+      <c r="AD75" s="148"/>
+      <c r="AE75" s="148"/>
+      <c r="AF75" s="148"/>
     </row>
     <row r="76" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="9"/>
@@ -9292,9 +9182,7 @@
       <c r="AF76" s="5"/>
     </row>
     <row r="77" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="67" t="s">
-        <v>63</v>
-      </c>
+      <c r="B77" s="67"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -9326,13 +9214,9 @@
     </row>
     <row r="78" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B78" s="4"/>
-      <c r="C78" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D78" s="292"/>
-      <c r="E78" s="111" t="s">
-        <v>60</v>
-      </c>
+      <c r="C78" s="154"/>
+      <c r="D78" s="155"/>
+      <c r="E78" s="111"/>
       <c r="F78" s="111"/>
       <c r="G78" s="111"/>
       <c r="H78" s="111"/>
@@ -9362,47 +9246,35 @@
     </row>
     <row r="79" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="4"/>
-      <c r="C79" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D79" s="292"/>
-      <c r="E79" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="F79" s="290"/>
-      <c r="G79" s="290"/>
-      <c r="H79" s="290"/>
-      <c r="I79" s="290"/>
-      <c r="J79" s="290"/>
-      <c r="K79" s="290"/>
-      <c r="L79" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="M79" s="292"/>
-      <c r="N79" s="111" t="s">
-        <v>67</v>
-      </c>
+      <c r="C79" s="154"/>
+      <c r="D79" s="155"/>
+      <c r="E79" s="152"/>
+      <c r="F79" s="153"/>
+      <c r="G79" s="153"/>
+      <c r="H79" s="153"/>
+      <c r="I79" s="153"/>
+      <c r="J79" s="153"/>
+      <c r="K79" s="153"/>
+      <c r="L79" s="154"/>
+      <c r="M79" s="155"/>
+      <c r="N79" s="111"/>
       <c r="O79" s="7"/>
       <c r="P79" s="7"/>
       <c r="Q79" s="111"/>
       <c r="S79" s="111"/>
-      <c r="T79" s="117" t="s">
-        <v>5</v>
-      </c>
-      <c r="U79" s="295" t="s">
-        <v>68</v>
-      </c>
-      <c r="V79" s="296"/>
-      <c r="W79" s="296"/>
-      <c r="X79" s="296"/>
-      <c r="Y79" s="296"/>
-      <c r="Z79" s="296"/>
-      <c r="AA79" s="296"/>
-      <c r="AB79" s="296"/>
-      <c r="AC79" s="296"/>
-      <c r="AD79" s="296"/>
-      <c r="AE79" s="296"/>
-      <c r="AF79" s="296"/>
+      <c r="T79" s="117"/>
+      <c r="U79" s="147"/>
+      <c r="V79" s="148"/>
+      <c r="W79" s="148"/>
+      <c r="X79" s="148"/>
+      <c r="Y79" s="148"/>
+      <c r="Z79" s="148"/>
+      <c r="AA79" s="148"/>
+      <c r="AB79" s="148"/>
+      <c r="AC79" s="148"/>
+      <c r="AD79" s="148"/>
+      <c r="AE79" s="148"/>
+      <c r="AF79" s="148"/>
     </row>
     <row r="80" spans="1:36" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="9"/>
@@ -9436,9 +9308,7 @@
       <c r="AF80" s="5"/>
     </row>
     <row r="81" spans="2:32" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="67" t="s">
-        <v>64</v>
-      </c>
+      <c r="B81" s="67"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -9470,13 +9340,9 @@
     </row>
     <row r="82" spans="2:32" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" s="4"/>
-      <c r="C82" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="292"/>
-      <c r="E82" s="111" t="s">
-        <v>60</v>
-      </c>
+      <c r="C82" s="154"/>
+      <c r="D82" s="155"/>
+      <c r="E82" s="111"/>
       <c r="F82" s="111"/>
       <c r="G82" s="111"/>
       <c r="H82" s="111"/>
@@ -9506,47 +9372,35 @@
     </row>
     <row r="83" spans="2:32" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="4"/>
-      <c r="C83" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="292"/>
-      <c r="E83" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="F83" s="290"/>
-      <c r="G83" s="290"/>
-      <c r="H83" s="290"/>
-      <c r="I83" s="290"/>
-      <c r="J83" s="290"/>
-      <c r="K83" s="290"/>
-      <c r="L83" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="292"/>
-      <c r="N83" s="111" t="s">
-        <v>67</v>
-      </c>
+      <c r="C83" s="154"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="152"/>
+      <c r="F83" s="153"/>
+      <c r="G83" s="153"/>
+      <c r="H83" s="153"/>
+      <c r="I83" s="153"/>
+      <c r="J83" s="153"/>
+      <c r="K83" s="153"/>
+      <c r="L83" s="154"/>
+      <c r="M83" s="155"/>
+      <c r="N83" s="111"/>
       <c r="O83" s="7"/>
       <c r="P83" s="7"/>
       <c r="Q83" s="111"/>
       <c r="S83" s="111"/>
-      <c r="T83" s="117" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="295" t="s">
-        <v>68</v>
-      </c>
-      <c r="V83" s="296"/>
-      <c r="W83" s="296"/>
-      <c r="X83" s="296"/>
-      <c r="Y83" s="296"/>
-      <c r="Z83" s="296"/>
-      <c r="AA83" s="296"/>
-      <c r="AB83" s="296"/>
-      <c r="AC83" s="296"/>
-      <c r="AD83" s="296"/>
-      <c r="AE83" s="296"/>
-      <c r="AF83" s="296"/>
+      <c r="T83" s="117"/>
+      <c r="U83" s="147"/>
+      <c r="V83" s="148"/>
+      <c r="W83" s="148"/>
+      <c r="X83" s="148"/>
+      <c r="Y83" s="148"/>
+      <c r="Z83" s="148"/>
+      <c r="AA83" s="148"/>
+      <c r="AB83" s="148"/>
+      <c r="AC83" s="148"/>
+      <c r="AD83" s="148"/>
+      <c r="AE83" s="148"/>
+      <c r="AF83" s="148"/>
     </row>
     <row r="84" spans="2:32" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" s="9"/>
@@ -9580,9 +9434,7 @@
       <c r="AF84" s="5"/>
     </row>
     <row r="85" spans="2:32" s="8" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="67" t="s">
-        <v>65</v>
-      </c>
+      <c r="B85" s="67"/>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
@@ -9616,13 +9468,9 @@
     </row>
     <row r="86" spans="2:32" s="63" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="4"/>
-      <c r="C86" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D86" s="292"/>
-      <c r="E86" s="111" t="s">
-        <v>60</v>
-      </c>
+      <c r="C86" s="154"/>
+      <c r="D86" s="155"/>
+      <c r="E86" s="111"/>
       <c r="F86" s="111"/>
       <c r="G86" s="111"/>
       <c r="H86" s="111"/>
@@ -9652,47 +9500,35 @@
     </row>
     <row r="87" spans="2:32" s="63" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="4"/>
-      <c r="C87" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D87" s="292"/>
-      <c r="E87" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="F87" s="290"/>
-      <c r="G87" s="290"/>
-      <c r="H87" s="290"/>
-      <c r="I87" s="290"/>
-      <c r="J87" s="290"/>
-      <c r="K87" s="290"/>
-      <c r="L87" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="M87" s="292"/>
-      <c r="N87" s="111" t="s">
-        <v>102</v>
-      </c>
+      <c r="C87" s="154"/>
+      <c r="D87" s="155"/>
+      <c r="E87" s="152"/>
+      <c r="F87" s="153"/>
+      <c r="G87" s="153"/>
+      <c r="H87" s="153"/>
+      <c r="I87" s="153"/>
+      <c r="J87" s="153"/>
+      <c r="K87" s="153"/>
+      <c r="L87" s="154"/>
+      <c r="M87" s="155"/>
+      <c r="N87" s="111"/>
       <c r="O87" s="7"/>
       <c r="P87" s="7"/>
       <c r="Q87" s="111"/>
       <c r="S87" s="111"/>
-      <c r="T87" s="117" t="s">
-        <v>5</v>
-      </c>
-      <c r="U87" s="295" t="s">
-        <v>68</v>
-      </c>
-      <c r="V87" s="296"/>
-      <c r="W87" s="296"/>
-      <c r="X87" s="296"/>
-      <c r="Y87" s="296"/>
-      <c r="Z87" s="296"/>
-      <c r="AA87" s="296"/>
-      <c r="AB87" s="296"/>
-      <c r="AC87" s="296"/>
-      <c r="AD87" s="296"/>
-      <c r="AE87" s="296"/>
-      <c r="AF87" s="296"/>
+      <c r="T87" s="117"/>
+      <c r="U87" s="147"/>
+      <c r="V87" s="148"/>
+      <c r="W87" s="148"/>
+      <c r="X87" s="148"/>
+      <c r="Y87" s="148"/>
+      <c r="Z87" s="148"/>
+      <c r="AA87" s="148"/>
+      <c r="AB87" s="148"/>
+      <c r="AC87" s="148"/>
+      <c r="AD87" s="148"/>
+      <c r="AE87" s="148"/>
+      <c r="AF87" s="148"/>
     </row>
     <row r="88" spans="2:32" s="63" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="64"/>
@@ -9727,9 +9563,7 @@
       <c r="AF88" s="12"/>
     </row>
     <row r="89" spans="2:32" s="63" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="68" t="s">
-        <v>66</v>
-      </c>
+      <c r="B89" s="68"/>
       <c r="C89" s="12"/>
       <c r="D89" s="12"/>
       <c r="E89" s="12"/>
@@ -9762,13 +9596,9 @@
     </row>
     <row r="90" spans="2:32" s="63" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="4"/>
-      <c r="C90" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D90" s="292"/>
-      <c r="E90" s="111" t="s">
-        <v>60</v>
-      </c>
+      <c r="C90" s="154"/>
+      <c r="D90" s="155"/>
+      <c r="E90" s="111"/>
       <c r="F90" s="111"/>
       <c r="G90" s="111"/>
       <c r="H90" s="111"/>
@@ -9798,47 +9628,35 @@
     </row>
     <row r="91" spans="2:32" s="63" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="4"/>
-      <c r="C91" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="D91" s="292"/>
-      <c r="E91" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="F91" s="290"/>
-      <c r="G91" s="290"/>
-      <c r="H91" s="290"/>
-      <c r="I91" s="290"/>
-      <c r="J91" s="290"/>
-      <c r="K91" s="290"/>
-      <c r="L91" s="291" t="s">
-        <v>5</v>
-      </c>
-      <c r="M91" s="292"/>
-      <c r="N91" s="111" t="s">
-        <v>67</v>
-      </c>
+      <c r="C91" s="154"/>
+      <c r="D91" s="155"/>
+      <c r="E91" s="152"/>
+      <c r="F91" s="153"/>
+      <c r="G91" s="153"/>
+      <c r="H91" s="153"/>
+      <c r="I91" s="153"/>
+      <c r="J91" s="153"/>
+      <c r="K91" s="153"/>
+      <c r="L91" s="154"/>
+      <c r="M91" s="155"/>
+      <c r="N91" s="111"/>
       <c r="O91" s="7"/>
       <c r="P91" s="7"/>
       <c r="Q91" s="111"/>
       <c r="S91" s="111"/>
-      <c r="T91" s="117" t="s">
-        <v>5</v>
-      </c>
-      <c r="U91" s="295" t="s">
-        <v>68</v>
-      </c>
-      <c r="V91" s="296"/>
-      <c r="W91" s="296"/>
-      <c r="X91" s="296"/>
-      <c r="Y91" s="296"/>
-      <c r="Z91" s="296"/>
-      <c r="AA91" s="296"/>
-      <c r="AB91" s="296"/>
-      <c r="AC91" s="296"/>
-      <c r="AD91" s="296"/>
-      <c r="AE91" s="296"/>
-      <c r="AF91" s="296"/>
+      <c r="T91" s="117"/>
+      <c r="U91" s="147"/>
+      <c r="V91" s="148"/>
+      <c r="W91" s="148"/>
+      <c r="X91" s="148"/>
+      <c r="Y91" s="148"/>
+      <c r="Z91" s="148"/>
+      <c r="AA91" s="148"/>
+      <c r="AB91" s="148"/>
+      <c r="AC91" s="148"/>
+      <c r="AD91" s="148"/>
+      <c r="AE91" s="148"/>
+      <c r="AF91" s="148"/>
     </row>
     <row r="92" spans="2:32" s="63" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B92" s="12"/>
@@ -10064,7 +9882,151 @@
     <row r="153" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" deleteRows="0"/>
-  <mergeCells count="163">
+  <mergeCells count="168">
+    <mergeCell ref="V49:W49"/>
+    <mergeCell ref="S50:U50"/>
+    <mergeCell ref="V50:W50"/>
+    <mergeCell ref="S51:U51"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="I6:Q6"/>
+    <mergeCell ref="M25:P26"/>
+    <mergeCell ref="M27:P28"/>
+    <mergeCell ref="M29:P30"/>
+    <mergeCell ref="M31:P32"/>
+    <mergeCell ref="M33:P34"/>
+    <mergeCell ref="S47:U47"/>
+    <mergeCell ref="V47:W47"/>
+    <mergeCell ref="S48:U48"/>
+    <mergeCell ref="V48:W48"/>
+    <mergeCell ref="X52:AA52"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:H32"/>
+    <mergeCell ref="I31:L32"/>
+    <mergeCell ref="Q31:T32"/>
+    <mergeCell ref="U31:W32"/>
+    <mergeCell ref="X31:AA32"/>
+    <mergeCell ref="M38:P38"/>
+    <mergeCell ref="Q38:T38"/>
+    <mergeCell ref="U38:W38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="Q39:T39"/>
+    <mergeCell ref="U39:W39"/>
+    <mergeCell ref="X39:AA39"/>
+    <mergeCell ref="H51:Q51"/>
+    <mergeCell ref="X46:AA46"/>
+    <mergeCell ref="X36:AA36"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:H34"/>
+    <mergeCell ref="I33:L34"/>
+    <mergeCell ref="S46:W46"/>
+    <mergeCell ref="H46:R46"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H47:R47"/>
+    <mergeCell ref="H48:R48"/>
+    <mergeCell ref="B41:W41"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="B43:AF43"/>
+    <mergeCell ref="X47:AA47"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="AB46:AE46"/>
+    <mergeCell ref="H49:R49"/>
+    <mergeCell ref="H50:R50"/>
+    <mergeCell ref="AB49:AE49"/>
+    <mergeCell ref="X50:AA50"/>
+    <mergeCell ref="AB50:AE50"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="S49:U49"/>
+    <mergeCell ref="AB39:AE39"/>
+    <mergeCell ref="AB31:AE32"/>
+    <mergeCell ref="AB36:AE36"/>
+    <mergeCell ref="X38:AA38"/>
+    <mergeCell ref="AB38:AE38"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="AF31:AF32"/>
+    <mergeCell ref="X35:AA35"/>
+    <mergeCell ref="AB35:AE35"/>
+    <mergeCell ref="X37:AA37"/>
+    <mergeCell ref="AB33:AE34"/>
+    <mergeCell ref="C35:W35"/>
+    <mergeCell ref="X51:AA51"/>
+    <mergeCell ref="AB51:AE51"/>
+    <mergeCell ref="X49:AA49"/>
+    <mergeCell ref="AF25:AF26"/>
+    <mergeCell ref="Q27:T28"/>
+    <mergeCell ref="U27:W28"/>
+    <mergeCell ref="X27:AA28"/>
+    <mergeCell ref="AB27:AE28"/>
+    <mergeCell ref="AF27:AF28"/>
+    <mergeCell ref="U36:W36"/>
+    <mergeCell ref="J36:S36"/>
+    <mergeCell ref="Q33:T34"/>
+    <mergeCell ref="U33:W34"/>
+    <mergeCell ref="AF29:AF30"/>
+    <mergeCell ref="AB47:AE47"/>
+    <mergeCell ref="X48:AA48"/>
+    <mergeCell ref="AB48:AE48"/>
+    <mergeCell ref="X40:AA40"/>
+    <mergeCell ref="X41:AA41"/>
+    <mergeCell ref="X33:AA34"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="AF33:AF34"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:H30"/>
+    <mergeCell ref="I29:L30"/>
+    <mergeCell ref="Q29:T30"/>
+    <mergeCell ref="U29:W30"/>
+    <mergeCell ref="X29:AA30"/>
+    <mergeCell ref="AB25:AE26"/>
+    <mergeCell ref="C25:H26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:H28"/>
+    <mergeCell ref="I27:L28"/>
+    <mergeCell ref="I25:L26"/>
+    <mergeCell ref="Q25:T26"/>
+    <mergeCell ref="U25:W26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="X25:AA26"/>
+    <mergeCell ref="AB29:AE30"/>
+    <mergeCell ref="W2:AD2"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="X24:AA24"/>
+    <mergeCell ref="AB24:AE24"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="V6:AB6"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="A8:AF8"/>
+    <mergeCell ref="A10:AF10"/>
+    <mergeCell ref="A12:AF12"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="A16:AF16"/>
+    <mergeCell ref="B21:AF21"/>
+    <mergeCell ref="A11:AF11"/>
+    <mergeCell ref="J2:R2"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="L83:M83"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="B52:W52"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="E67:K67"/>
+    <mergeCell ref="E71:K71"/>
+    <mergeCell ref="L71:M71"/>
+    <mergeCell ref="E75:K75"/>
+    <mergeCell ref="L75:M75"/>
     <mergeCell ref="U91:AF91"/>
     <mergeCell ref="B56:AF56"/>
     <mergeCell ref="U67:AF67"/>
@@ -10089,154 +10051,15 @@
     <mergeCell ref="L79:M79"/>
     <mergeCell ref="B58:AF58"/>
     <mergeCell ref="H61:AF61"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="L83:M83"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="B52:W52"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="E67:K67"/>
-    <mergeCell ref="E71:K71"/>
-    <mergeCell ref="L71:M71"/>
-    <mergeCell ref="E75:K75"/>
-    <mergeCell ref="L75:M75"/>
-    <mergeCell ref="W2:AD2"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:T24"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="X24:AA24"/>
-    <mergeCell ref="AB24:AE24"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="V6:AB6"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="O4:U4"/>
-    <mergeCell ref="A8:AF8"/>
-    <mergeCell ref="A10:AF10"/>
-    <mergeCell ref="A12:AF12"/>
-    <mergeCell ref="A13:AF13"/>
-    <mergeCell ref="A16:AF16"/>
-    <mergeCell ref="B21:AF21"/>
-    <mergeCell ref="A11:AF11"/>
-    <mergeCell ref="J2:R2"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:H30"/>
-    <mergeCell ref="I29:L30"/>
-    <mergeCell ref="Q29:T30"/>
-    <mergeCell ref="U29:W30"/>
-    <mergeCell ref="X29:AA30"/>
-    <mergeCell ref="AB25:AE26"/>
-    <mergeCell ref="C25:H26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:H28"/>
-    <mergeCell ref="I27:L28"/>
-    <mergeCell ref="I25:L26"/>
-    <mergeCell ref="Q25:T26"/>
-    <mergeCell ref="U25:W26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="X25:AA26"/>
-    <mergeCell ref="AB29:AE30"/>
-    <mergeCell ref="M25:P26"/>
-    <mergeCell ref="M27:P28"/>
-    <mergeCell ref="M29:P30"/>
-    <mergeCell ref="X51:AA51"/>
-    <mergeCell ref="AB51:AE51"/>
-    <mergeCell ref="X49:AA49"/>
-    <mergeCell ref="AF25:AF26"/>
-    <mergeCell ref="I6:P6"/>
-    <mergeCell ref="Q27:T28"/>
-    <mergeCell ref="U27:W28"/>
-    <mergeCell ref="X27:AA28"/>
-    <mergeCell ref="AB27:AE28"/>
-    <mergeCell ref="AF27:AF28"/>
-    <mergeCell ref="U36:W36"/>
-    <mergeCell ref="J36:S36"/>
-    <mergeCell ref="Q33:T34"/>
-    <mergeCell ref="U33:W34"/>
-    <mergeCell ref="AF29:AF30"/>
-    <mergeCell ref="AB47:AE47"/>
-    <mergeCell ref="X48:AA48"/>
-    <mergeCell ref="AB48:AE48"/>
-    <mergeCell ref="X40:AA40"/>
-    <mergeCell ref="X41:AA41"/>
-    <mergeCell ref="X33:AA34"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="AF33:AF34"/>
-    <mergeCell ref="AB39:AE39"/>
-    <mergeCell ref="AB31:AE32"/>
-    <mergeCell ref="AB36:AE36"/>
-    <mergeCell ref="X38:AA38"/>
-    <mergeCell ref="AB38:AE38"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="AF31:AF32"/>
-    <mergeCell ref="X35:AA35"/>
-    <mergeCell ref="AB35:AE35"/>
-    <mergeCell ref="X37:AA37"/>
-    <mergeCell ref="AB33:AE34"/>
-    <mergeCell ref="C35:W35"/>
-    <mergeCell ref="M31:P32"/>
-    <mergeCell ref="M33:P34"/>
-    <mergeCell ref="S46:W46"/>
-    <mergeCell ref="H46:R46"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H47:R47"/>
-    <mergeCell ref="H48:R48"/>
-    <mergeCell ref="B41:W41"/>
-    <mergeCell ref="S48:W48"/>
-    <mergeCell ref="S49:W49"/>
-    <mergeCell ref="S50:W50"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="B43:AF43"/>
-    <mergeCell ref="X47:AA47"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="H49:R49"/>
-    <mergeCell ref="H50:R50"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="AB49:AE49"/>
-    <mergeCell ref="X50:AA50"/>
-    <mergeCell ref="AB50:AE50"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="X52:AA52"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:H32"/>
-    <mergeCell ref="I31:L32"/>
-    <mergeCell ref="Q31:T32"/>
-    <mergeCell ref="U31:W32"/>
-    <mergeCell ref="X31:AA32"/>
-    <mergeCell ref="M38:P38"/>
-    <mergeCell ref="Q38:T38"/>
-    <mergeCell ref="U38:W38"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:P39"/>
-    <mergeCell ref="Q39:T39"/>
-    <mergeCell ref="U39:W39"/>
-    <mergeCell ref="X39:AA39"/>
-    <mergeCell ref="H51:Q51"/>
-    <mergeCell ref="X46:AA46"/>
-    <mergeCell ref="S51:W51"/>
-    <mergeCell ref="X36:AA36"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:H34"/>
-    <mergeCell ref="I33:L34"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="I6">
-    <cfRule type="containsBlanks" dxfId="3" priority="15">
+    <cfRule type="containsBlanks" dxfId="5" priority="15">
       <formula>LEN(TRIM(I6))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4">
-    <cfRule type="containsBlanks" dxfId="2" priority="16">
+    <cfRule type="containsBlanks" dxfId="3" priority="16">
       <formula>LEN(TRIM(O4))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10250,14 +10073,18 @@
       <formula>LEN(TRIM(W2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20 I20 Q20 L91 C78:C79 T79 C90:C91 T91 L67 L71 L75 L79 L83 M42 L87 AF47:AF51 M45 B44 I44 Q44 C66:C67 T67 C74:C75 T75 C82:C83 T83 C86:C87 T87 C70:C71 T71" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20 I20 Q20 M42 L87 L91 L79 AF25 AF27 AF29 AF33 AF35:AF36 AF31 AF38:AF39 L83 AF47:AF51 M45 B44 I44 Q44 C66:C67 T67 C74:C75 T75 C82:C83 T83 C86:C87 T87 C70:C71 T71 C78:C79 T79 C90:C91 T91 L67 L71 L75" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"□,■"</formula1>
     </dataValidation>
-    <dataValidation imeMode="hiragana" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:AD2 AB47:AE51 C47:R51 V6" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
-    <dataValidation imeMode="fullAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S47:AA51" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45 B82:B83 B74:B75 U91 B70:B71 E59:E67 B78:B79 B86:B87 P63:AE65 N71 E90:E91 AF63:AF66 N67 C59:D65 E70:E71 N75 E74:E75 I62:O66 N79 E78:E79 N83 N87 E86:E87 E82:E83 B90:B91 F59:H66 Q71 N91 U79 U71 U75 U67 Q87 T70:AF70 F70:Q70 T78:AF78 F78:Q78 T74:AF74 F74:Q74 T82:AF82 F82:Q82 T66:AE66 P66:Q66 S82:S83 Q83 S78:S79 Q79 S74:S75 Q75 S66:S67 Q67 S70:S71 U87 U83 T86:AF86 F86:Q86 T90:AF90 F90:Q90 S90:S91 Q91 S86:S87 P62 I59:N60 O60:Q60 P59 B52:B67 C53:AA55 AB52:AF55 AG47:AG67 B42:B43" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="日付を入力してください_x000a_令和６年４月１日 と入力_x000a_する場合は　r6/4/1 または_x000a_　24/4/1 " sqref="I6:O6 O4" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
+    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q25:T34 Q38:T39" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation imeMode="hiragana" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:AD2 AB47:AE51 C47:R51 M27:P34 C38:L39 AB25:AE40 V6 J36:S36 C25:L34" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
+    <dataValidation imeMode="fullAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X25:AA36 X38:AA39 X47:AA51 V47:V51 S47:S51" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
+    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45 B82:B83 B74:B75 U91 B70:B71 E59:E67 B78:B79 B86:B87 P63:AE65 N71 E90:E91 AF63:AF66 N67 C59:D65 E70:E71 N75 E74:E75 I62:O66 N79 E78:E79 N83 N87 E86:E87 E82:E83 B90:B91 F59:H66 Q71 N91 U79 U71 U75 U67 Q87 T70:AF70 F70:Q70 T78:AF78 F78:Q78 T74:AF74 F74:Q74 T82:AF82 F82:Q82 T66:AE66 P66:Q66 S82:S83 Q83 S78:S79 Q79 S74:S75 Q75 S66:S67 Q67 S70:S71 U87 U83 T86:AF86 F86:Q86 T90:AF90 F90:Q90 S90:S91 Q91 S86:S87 P62 I59:N60 O60:Q60 P59 B52:B67 C53:AA55 AB52:AF55 B25:B43 AG47:AG67" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
+    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="日付を入力してください_x000a_令和６年４月１日 と入力_x000a_する場合は　r6/4/1 または_x000a_　24/4/1 " sqref="O4 I6" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
+    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="日付を入力してください。" prompt="今年の４月１日なら4/1と入力_x000a_今年の日付でないなら年も入力_x000a_(令和5年４月１日の場合は_x000a_　r5/4/1 または　23/4/1)" sqref="U38:W39 U25:W34" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
+    <dataValidation imeMode="off" allowBlank="1" showErrorMessage="1" sqref="U36:W36" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="C35:W35" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
   </dataValidations>
   <pageMargins left="0.78740157480314965" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" cellComments="asDisplayed" r:id="rId1"/>
@@ -10301,7 +10128,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="15.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" s="81"/>
       <c r="C1" s="61"/>
@@ -10351,7 +10178,7 @@
     </row>
     <row r="3" spans="1:22" s="61" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -10377,26 +10204,26 @@
     <row r="4" spans="1:22" s="61" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
       <c r="B4" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="L4" s="10"/>
       <c r="M4" s="3"/>
@@ -10434,192 +10261,192 @@
     </row>
     <row r="6" spans="1:22" s="61" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="372" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="373"/>
-      <c r="D6" s="405"/>
-      <c r="E6" s="372" t="s">
+      <c r="B6" s="300" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="373"/>
-      <c r="G6" s="405"/>
-      <c r="H6" s="372" t="s">
+      <c r="C6" s="301"/>
+      <c r="D6" s="319"/>
+      <c r="E6" s="300" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="405"/>
-      <c r="J6" s="406" t="s">
-        <v>95</v>
-      </c>
-      <c r="K6" s="406"/>
-      <c r="L6" s="407"/>
-      <c r="M6" s="303" t="s">
+      <c r="F6" s="301"/>
+      <c r="G6" s="319"/>
+      <c r="H6" s="300" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="304"/>
-      <c r="O6" s="304"/>
-      <c r="P6" s="304"/>
-      <c r="Q6" s="304"/>
-      <c r="R6" s="205"/>
-      <c r="S6" s="206"/>
-      <c r="T6" s="372" t="s">
+      <c r="I6" s="319"/>
+      <c r="J6" s="320" t="s">
+        <v>85</v>
+      </c>
+      <c r="K6" s="320"/>
+      <c r="L6" s="321"/>
+      <c r="M6" s="287" t="s">
         <v>17</v>
       </c>
-      <c r="U6" s="373"/>
+      <c r="N6" s="289"/>
+      <c r="O6" s="289"/>
+      <c r="P6" s="289"/>
+      <c r="Q6" s="289"/>
+      <c r="R6" s="264"/>
+      <c r="S6" s="265"/>
+      <c r="T6" s="300" t="s">
+        <v>18</v>
+      </c>
+      <c r="U6" s="301"/>
       <c r="V6" s="88" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="130">
         <v>1</v>
       </c>
-      <c r="B7" s="219"/>
-      <c r="C7" s="362"/>
-      <c r="D7" s="401"/>
-      <c r="E7" s="219"/>
-      <c r="F7" s="362"/>
-      <c r="G7" s="401"/>
-      <c r="H7" s="402"/>
-      <c r="I7" s="403"/>
-      <c r="J7" s="222"/>
-      <c r="K7" s="352"/>
-      <c r="L7" s="352"/>
-      <c r="M7" s="219"/>
-      <c r="N7" s="362"/>
-      <c r="O7" s="362"/>
-      <c r="P7" s="362"/>
-      <c r="Q7" s="362"/>
-      <c r="R7" s="209"/>
-      <c r="S7" s="210"/>
-      <c r="T7" s="355"/>
-      <c r="U7" s="404"/>
+      <c r="B7" s="240"/>
+      <c r="C7" s="290"/>
+      <c r="D7" s="313"/>
+      <c r="E7" s="240"/>
+      <c r="F7" s="290"/>
+      <c r="G7" s="313"/>
+      <c r="H7" s="314"/>
+      <c r="I7" s="315"/>
+      <c r="J7" s="270"/>
+      <c r="K7" s="316"/>
+      <c r="L7" s="316"/>
+      <c r="M7" s="240"/>
+      <c r="N7" s="290"/>
+      <c r="O7" s="290"/>
+      <c r="P7" s="290"/>
+      <c r="Q7" s="290"/>
+      <c r="R7" s="241"/>
+      <c r="S7" s="242"/>
+      <c r="T7" s="317"/>
+      <c r="U7" s="318"/>
       <c r="V7" s="133" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:22" s="96" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="131">
         <v>2</v>
       </c>
-      <c r="B8" s="381"/>
-      <c r="C8" s="382"/>
-      <c r="D8" s="383"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="344"/>
-      <c r="G8" s="389"/>
-      <c r="H8" s="390"/>
-      <c r="I8" s="391"/>
-      <c r="J8" s="228"/>
-      <c r="K8" s="350"/>
-      <c r="L8" s="358"/>
-      <c r="M8" s="207"/>
-      <c r="N8" s="344"/>
-      <c r="O8" s="344"/>
-      <c r="P8" s="344"/>
-      <c r="Q8" s="344"/>
-      <c r="R8" s="186"/>
-      <c r="S8" s="187"/>
+      <c r="B8" s="302"/>
+      <c r="C8" s="303"/>
+      <c r="D8" s="304"/>
+      <c r="E8" s="243"/>
+      <c r="F8" s="305"/>
+      <c r="G8" s="306"/>
+      <c r="H8" s="307"/>
+      <c r="I8" s="308"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="309"/>
+      <c r="L8" s="310"/>
+      <c r="M8" s="243"/>
+      <c r="N8" s="305"/>
+      <c r="O8" s="305"/>
+      <c r="P8" s="305"/>
+      <c r="Q8" s="305"/>
+      <c r="R8" s="239"/>
+      <c r="S8" s="244"/>
       <c r="T8" s="311"/>
-      <c r="U8" s="392"/>
+      <c r="U8" s="312"/>
       <c r="V8" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="131">
         <v>3</v>
       </c>
-      <c r="B9" s="207" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="344"/>
-      <c r="D9" s="389"/>
-      <c r="E9" s="207"/>
-      <c r="F9" s="344"/>
-      <c r="G9" s="344"/>
-      <c r="H9" s="390"/>
-      <c r="I9" s="391"/>
-      <c r="J9" s="228" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" s="350"/>
-      <c r="L9" s="358"/>
-      <c r="M9" s="207"/>
-      <c r="N9" s="344"/>
-      <c r="O9" s="344"/>
-      <c r="P9" s="344"/>
-      <c r="Q9" s="344"/>
-      <c r="R9" s="186"/>
-      <c r="S9" s="187"/>
+      <c r="B9" s="243" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="305"/>
+      <c r="D9" s="306"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="305"/>
+      <c r="H9" s="307"/>
+      <c r="I9" s="308"/>
+      <c r="J9" s="229" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="309"/>
+      <c r="L9" s="310"/>
+      <c r="M9" s="243"/>
+      <c r="N9" s="305"/>
+      <c r="O9" s="305"/>
+      <c r="P9" s="305"/>
+      <c r="Q9" s="305"/>
+      <c r="R9" s="239"/>
+      <c r="S9" s="244"/>
       <c r="T9" s="311"/>
-      <c r="U9" s="392"/>
+      <c r="U9" s="312"/>
       <c r="V9" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="131">
         <v>4</v>
       </c>
-      <c r="B10" s="381"/>
-      <c r="C10" s="382"/>
-      <c r="D10" s="383"/>
-      <c r="E10" s="381"/>
-      <c r="F10" s="382"/>
-      <c r="G10" s="383"/>
-      <c r="H10" s="384"/>
-      <c r="I10" s="385"/>
-      <c r="J10" s="386"/>
-      <c r="K10" s="387"/>
-      <c r="L10" s="388"/>
-      <c r="M10" s="207"/>
-      <c r="N10" s="344"/>
-      <c r="O10" s="344"/>
-      <c r="P10" s="344"/>
-      <c r="Q10" s="344"/>
-      <c r="R10" s="186"/>
-      <c r="S10" s="187"/>
-      <c r="T10" s="393"/>
-      <c r="U10" s="394"/>
+      <c r="B10" s="302"/>
+      <c r="C10" s="303"/>
+      <c r="D10" s="304"/>
+      <c r="E10" s="302"/>
+      <c r="F10" s="303"/>
+      <c r="G10" s="304"/>
+      <c r="H10" s="335"/>
+      <c r="I10" s="336"/>
+      <c r="J10" s="337"/>
+      <c r="K10" s="338"/>
+      <c r="L10" s="339"/>
+      <c r="M10" s="243"/>
+      <c r="N10" s="305"/>
+      <c r="O10" s="305"/>
+      <c r="P10" s="305"/>
+      <c r="Q10" s="305"/>
+      <c r="R10" s="239"/>
+      <c r="S10" s="244"/>
+      <c r="T10" s="340"/>
+      <c r="U10" s="341"/>
       <c r="V10" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="137">
         <v>5</v>
       </c>
-      <c r="B11" s="340" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="341"/>
-      <c r="D11" s="374"/>
-      <c r="E11" s="340"/>
-      <c r="F11" s="341"/>
-      <c r="G11" s="341"/>
-      <c r="H11" s="375" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="376"/>
-      <c r="J11" s="359"/>
-      <c r="K11" s="360"/>
-      <c r="L11" s="361"/>
-      <c r="M11" s="340" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="341"/>
-      <c r="O11" s="341"/>
-      <c r="P11" s="341"/>
-      <c r="Q11" s="341"/>
-      <c r="R11" s="356"/>
-      <c r="S11" s="342"/>
-      <c r="T11" s="326"/>
-      <c r="U11" s="377"/>
+      <c r="B11" s="342" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="343"/>
+      <c r="D11" s="344"/>
+      <c r="E11" s="342"/>
+      <c r="F11" s="343"/>
+      <c r="G11" s="343"/>
+      <c r="H11" s="345" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="346"/>
+      <c r="J11" s="347"/>
+      <c r="K11" s="348"/>
+      <c r="L11" s="349"/>
+      <c r="M11" s="342" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="343"/>
+      <c r="O11" s="343"/>
+      <c r="P11" s="343"/>
+      <c r="Q11" s="343"/>
+      <c r="R11" s="355"/>
+      <c r="S11" s="356"/>
+      <c r="T11" s="350"/>
+      <c r="U11" s="351"/>
       <c r="V11" s="138" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:22" s="61" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -10629,7 +10456,7 @@
     </row>
     <row r="13" spans="1:22" s="61" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -10655,26 +10482,26 @@
     <row r="14" spans="1:22" s="61" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
       <c r="B14" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
       <c r="J14" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="L14" s="10"/>
       <c r="M14" s="3"/>
@@ -10712,180 +10539,180 @@
     </row>
     <row r="16" spans="1:22" s="61" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="371" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="371"/>
-      <c r="D16" s="371"/>
-      <c r="E16" s="371"/>
-      <c r="F16" s="371"/>
-      <c r="G16" s="371"/>
-      <c r="H16" s="371" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="297" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="371"/>
-      <c r="J16" s="372" t="s">
+      <c r="C16" s="297"/>
+      <c r="D16" s="297"/>
+      <c r="E16" s="297"/>
+      <c r="F16" s="297"/>
+      <c r="G16" s="297"/>
+      <c r="H16" s="297" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="373"/>
-      <c r="L16" s="373"/>
-      <c r="M16" s="378" t="s">
+      <c r="I16" s="297"/>
+      <c r="J16" s="300" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="379"/>
-      <c r="O16" s="379"/>
-      <c r="P16" s="379"/>
-      <c r="Q16" s="379"/>
-      <c r="R16" s="380"/>
-      <c r="S16" s="308" t="s">
-        <v>96</v>
-      </c>
-      <c r="T16" s="309"/>
-      <c r="U16" s="310"/>
+      <c r="K16" s="301"/>
+      <c r="L16" s="301"/>
+      <c r="M16" s="352" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="353"/>
+      <c r="O16" s="353"/>
+      <c r="P16" s="353"/>
+      <c r="Q16" s="353"/>
+      <c r="R16" s="354"/>
+      <c r="S16" s="357" t="s">
+        <v>86</v>
+      </c>
+      <c r="T16" s="358"/>
+      <c r="U16" s="359"/>
       <c r="V16" s="88" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="130">
         <v>1</v>
       </c>
-      <c r="B17" s="345"/>
-      <c r="C17" s="345"/>
-      <c r="D17" s="345"/>
-      <c r="E17" s="345"/>
-      <c r="F17" s="345"/>
-      <c r="G17" s="345"/>
-      <c r="H17" s="346"/>
-      <c r="I17" s="346"/>
-      <c r="J17" s="395"/>
-      <c r="K17" s="396"/>
-      <c r="L17" s="396"/>
-      <c r="M17" s="320"/>
-      <c r="N17" s="321"/>
-      <c r="O17" s="321"/>
-      <c r="P17" s="321"/>
-      <c r="Q17" s="321"/>
-      <c r="R17" s="322"/>
-      <c r="S17" s="355"/>
-      <c r="T17" s="324"/>
-      <c r="U17" s="325"/>
+      <c r="B17" s="322"/>
+      <c r="C17" s="322"/>
+      <c r="D17" s="322"/>
+      <c r="E17" s="322"/>
+      <c r="F17" s="322"/>
+      <c r="G17" s="322"/>
+      <c r="H17" s="285"/>
+      <c r="I17" s="285"/>
+      <c r="J17" s="323"/>
+      <c r="K17" s="324"/>
+      <c r="L17" s="324"/>
+      <c r="M17" s="325"/>
+      <c r="N17" s="326"/>
+      <c r="O17" s="326"/>
+      <c r="P17" s="326"/>
+      <c r="Q17" s="326"/>
+      <c r="R17" s="327"/>
+      <c r="S17" s="317"/>
+      <c r="T17" s="331"/>
+      <c r="U17" s="332"/>
       <c r="V17" s="133" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="131">
         <v>2</v>
       </c>
-      <c r="B18" s="397"/>
-      <c r="C18" s="397"/>
-      <c r="D18" s="397"/>
-      <c r="E18" s="397"/>
-      <c r="F18" s="397"/>
-      <c r="G18" s="397"/>
-      <c r="H18" s="398"/>
-      <c r="I18" s="398"/>
-      <c r="J18" s="399"/>
-      <c r="K18" s="400"/>
-      <c r="L18" s="400"/>
-      <c r="M18" s="305"/>
-      <c r="N18" s="306"/>
-      <c r="O18" s="306"/>
-      <c r="P18" s="306"/>
-      <c r="Q18" s="306"/>
-      <c r="R18" s="307"/>
+      <c r="B18" s="293"/>
+      <c r="C18" s="293"/>
+      <c r="D18" s="293"/>
+      <c r="E18" s="293"/>
+      <c r="F18" s="293"/>
+      <c r="G18" s="293"/>
+      <c r="H18" s="294"/>
+      <c r="I18" s="294"/>
+      <c r="J18" s="295"/>
+      <c r="K18" s="296"/>
+      <c r="L18" s="296"/>
+      <c r="M18" s="328"/>
+      <c r="N18" s="329"/>
+      <c r="O18" s="329"/>
+      <c r="P18" s="329"/>
+      <c r="Q18" s="329"/>
+      <c r="R18" s="330"/>
       <c r="S18" s="311"/>
-      <c r="T18" s="312"/>
-      <c r="U18" s="313"/>
+      <c r="T18" s="333"/>
+      <c r="U18" s="334"/>
       <c r="V18" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="131">
         <v>3</v>
       </c>
-      <c r="B19" s="397"/>
-      <c r="C19" s="397"/>
-      <c r="D19" s="397"/>
-      <c r="E19" s="397"/>
-      <c r="F19" s="397"/>
-      <c r="G19" s="397"/>
-      <c r="H19" s="398"/>
-      <c r="I19" s="398"/>
-      <c r="J19" s="399"/>
-      <c r="K19" s="400"/>
-      <c r="L19" s="400"/>
-      <c r="M19" s="305"/>
-      <c r="N19" s="306"/>
-      <c r="O19" s="306"/>
-      <c r="P19" s="306"/>
-      <c r="Q19" s="306"/>
-      <c r="R19" s="307"/>
+      <c r="B19" s="293"/>
+      <c r="C19" s="293"/>
+      <c r="D19" s="293"/>
+      <c r="E19" s="293"/>
+      <c r="F19" s="293"/>
+      <c r="G19" s="293"/>
+      <c r="H19" s="294"/>
+      <c r="I19" s="294"/>
+      <c r="J19" s="295"/>
+      <c r="K19" s="296"/>
+      <c r="L19" s="296"/>
+      <c r="M19" s="328"/>
+      <c r="N19" s="329"/>
+      <c r="O19" s="329"/>
+      <c r="P19" s="329"/>
+      <c r="Q19" s="329"/>
+      <c r="R19" s="330"/>
       <c r="S19" s="311"/>
-      <c r="T19" s="312"/>
-      <c r="U19" s="313"/>
+      <c r="T19" s="333"/>
+      <c r="U19" s="334"/>
       <c r="V19" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="131">
         <v>4</v>
       </c>
-      <c r="B20" s="397"/>
-      <c r="C20" s="397"/>
-      <c r="D20" s="397"/>
-      <c r="E20" s="397"/>
-      <c r="F20" s="397"/>
-      <c r="G20" s="397"/>
-      <c r="H20" s="398"/>
-      <c r="I20" s="398"/>
-      <c r="J20" s="399"/>
-      <c r="K20" s="400"/>
-      <c r="L20" s="400"/>
-      <c r="M20" s="305"/>
-      <c r="N20" s="306"/>
-      <c r="O20" s="306"/>
-      <c r="P20" s="306"/>
-      <c r="Q20" s="306"/>
-      <c r="R20" s="307"/>
+      <c r="B20" s="293"/>
+      <c r="C20" s="293"/>
+      <c r="D20" s="293"/>
+      <c r="E20" s="293"/>
+      <c r="F20" s="293"/>
+      <c r="G20" s="293"/>
+      <c r="H20" s="294"/>
+      <c r="I20" s="294"/>
+      <c r="J20" s="295"/>
+      <c r="K20" s="296"/>
+      <c r="L20" s="296"/>
+      <c r="M20" s="328"/>
+      <c r="N20" s="329"/>
+      <c r="O20" s="329"/>
+      <c r="P20" s="329"/>
+      <c r="Q20" s="329"/>
+      <c r="R20" s="330"/>
       <c r="S20" s="311"/>
-      <c r="T20" s="312"/>
-      <c r="U20" s="313"/>
+      <c r="T20" s="333"/>
+      <c r="U20" s="334"/>
       <c r="V20" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="137">
         <v>5</v>
       </c>
-      <c r="B21" s="408"/>
-      <c r="C21" s="408"/>
-      <c r="D21" s="408"/>
-      <c r="E21" s="408"/>
-      <c r="F21" s="408"/>
-      <c r="G21" s="408"/>
-      <c r="H21" s="409"/>
-      <c r="I21" s="409"/>
-      <c r="J21" s="410"/>
-      <c r="K21" s="411"/>
-      <c r="L21" s="411"/>
-      <c r="M21" s="317"/>
-      <c r="N21" s="318"/>
-      <c r="O21" s="318"/>
-      <c r="P21" s="318"/>
-      <c r="Q21" s="318"/>
-      <c r="R21" s="319"/>
-      <c r="S21" s="326"/>
-      <c r="T21" s="315"/>
-      <c r="U21" s="316"/>
+      <c r="B21" s="288"/>
+      <c r="C21" s="288"/>
+      <c r="D21" s="288"/>
+      <c r="E21" s="288"/>
+      <c r="F21" s="288"/>
+      <c r="G21" s="288"/>
+      <c r="H21" s="286"/>
+      <c r="I21" s="286"/>
+      <c r="J21" s="298"/>
+      <c r="K21" s="299"/>
+      <c r="L21" s="299"/>
+      <c r="M21" s="375"/>
+      <c r="N21" s="376"/>
+      <c r="O21" s="376"/>
+      <c r="P21" s="376"/>
+      <c r="Q21" s="376"/>
+      <c r="R21" s="377"/>
+      <c r="S21" s="350"/>
+      <c r="T21" s="373"/>
+      <c r="U21" s="374"/>
       <c r="V21" s="138" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:22" s="61" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -10912,7 +10739,7 @@
     </row>
     <row r="23" spans="1:22" s="61" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -10938,26 +10765,26 @@
     <row r="24" spans="1:22" s="61" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
       <c r="J24" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="L24" s="10"/>
       <c r="M24" s="3"/>
@@ -10995,196 +10822,196 @@
     </row>
     <row r="26" spans="1:22" s="61" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="371" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="371"/>
-      <c r="D26" s="371"/>
-      <c r="E26" s="371"/>
-      <c r="F26" s="371"/>
-      <c r="G26" s="371"/>
-      <c r="H26" s="371" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="371"/>
-      <c r="J26" s="371" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="297" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="297"/>
+      <c r="D26" s="297"/>
+      <c r="E26" s="297"/>
+      <c r="F26" s="297"/>
+      <c r="G26" s="297"/>
+      <c r="H26" s="297" t="s">
         <v>25</v>
       </c>
-      <c r="K26" s="371"/>
-      <c r="L26" s="371"/>
-      <c r="M26" s="303" t="s">
+      <c r="I26" s="297"/>
+      <c r="J26" s="297" t="s">
         <v>26</v>
       </c>
-      <c r="N26" s="304"/>
-      <c r="O26" s="304"/>
-      <c r="P26" s="304"/>
-      <c r="Q26" s="304"/>
-      <c r="R26" s="206"/>
-      <c r="S26" s="308" t="s">
-        <v>96</v>
-      </c>
-      <c r="T26" s="309"/>
-      <c r="U26" s="310"/>
+      <c r="K26" s="297"/>
+      <c r="L26" s="297"/>
+      <c r="M26" s="287" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="289"/>
+      <c r="O26" s="289"/>
+      <c r="P26" s="289"/>
+      <c r="Q26" s="289"/>
+      <c r="R26" s="265"/>
+      <c r="S26" s="357" t="s">
+        <v>86</v>
+      </c>
+      <c r="T26" s="358"/>
+      <c r="U26" s="359"/>
       <c r="V26" s="88" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="130">
         <v>1</v>
       </c>
-      <c r="B27" s="345"/>
-      <c r="C27" s="345"/>
-      <c r="D27" s="345"/>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
-      <c r="G27" s="345"/>
-      <c r="H27" s="346"/>
-      <c r="I27" s="346"/>
-      <c r="J27" s="346"/>
-      <c r="K27" s="346"/>
-      <c r="L27" s="346"/>
-      <c r="M27" s="320"/>
-      <c r="N27" s="321"/>
-      <c r="O27" s="321"/>
-      <c r="P27" s="321"/>
-      <c r="Q27" s="321"/>
-      <c r="R27" s="322"/>
-      <c r="S27" s="323"/>
-      <c r="T27" s="324"/>
-      <c r="U27" s="325"/>
+      <c r="B27" s="322"/>
+      <c r="C27" s="322"/>
+      <c r="D27" s="322"/>
+      <c r="E27" s="322"/>
+      <c r="F27" s="322"/>
+      <c r="G27" s="322"/>
+      <c r="H27" s="285"/>
+      <c r="I27" s="285"/>
+      <c r="J27" s="285"/>
+      <c r="K27" s="285"/>
+      <c r="L27" s="285"/>
+      <c r="M27" s="325"/>
+      <c r="N27" s="326"/>
+      <c r="O27" s="326"/>
+      <c r="P27" s="326"/>
+      <c r="Q27" s="326"/>
+      <c r="R27" s="327"/>
+      <c r="S27" s="390"/>
+      <c r="T27" s="331"/>
+      <c r="U27" s="332"/>
       <c r="V27" s="133" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="131">
         <v>2</v>
       </c>
-      <c r="B28" s="369"/>
-      <c r="C28" s="369"/>
-      <c r="D28" s="369"/>
-      <c r="E28" s="369"/>
-      <c r="F28" s="369"/>
-      <c r="G28" s="369"/>
-      <c r="H28" s="370"/>
-      <c r="I28" s="370"/>
-      <c r="J28" s="370" t="s">
-        <v>27</v>
-      </c>
-      <c r="K28" s="370"/>
-      <c r="L28" s="370"/>
-      <c r="M28" s="305"/>
-      <c r="N28" s="306"/>
-      <c r="O28" s="306"/>
-      <c r="P28" s="306"/>
-      <c r="Q28" s="306"/>
-      <c r="R28" s="307"/>
+      <c r="B28" s="291"/>
+      <c r="C28" s="291"/>
+      <c r="D28" s="291"/>
+      <c r="E28" s="291"/>
+      <c r="F28" s="291"/>
+      <c r="G28" s="291"/>
+      <c r="H28" s="292"/>
+      <c r="I28" s="292"/>
+      <c r="J28" s="292" t="s">
+        <v>28</v>
+      </c>
+      <c r="K28" s="292"/>
+      <c r="L28" s="292"/>
+      <c r="M28" s="328"/>
+      <c r="N28" s="329"/>
+      <c r="O28" s="329"/>
+      <c r="P28" s="329"/>
+      <c r="Q28" s="329"/>
+      <c r="R28" s="330"/>
       <c r="S28" s="311" t="s">
-        <v>18</v>
-      </c>
-      <c r="T28" s="312"/>
-      <c r="U28" s="313"/>
+        <v>19</v>
+      </c>
+      <c r="T28" s="333"/>
+      <c r="U28" s="334"/>
       <c r="V28" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="131">
         <v>3</v>
       </c>
-      <c r="B29" s="397" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="397"/>
-      <c r="D29" s="397"/>
-      <c r="E29" s="397"/>
-      <c r="F29" s="397"/>
-      <c r="G29" s="397"/>
-      <c r="H29" s="398"/>
-      <c r="I29" s="398"/>
-      <c r="J29" s="398" t="s">
-        <v>27</v>
-      </c>
-      <c r="K29" s="398"/>
-      <c r="L29" s="398"/>
-      <c r="M29" s="305"/>
-      <c r="N29" s="306"/>
-      <c r="O29" s="306"/>
-      <c r="P29" s="306"/>
-      <c r="Q29" s="306"/>
-      <c r="R29" s="307"/>
+      <c r="B29" s="293" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="293"/>
+      <c r="D29" s="293"/>
+      <c r="E29" s="293"/>
+      <c r="F29" s="293"/>
+      <c r="G29" s="293"/>
+      <c r="H29" s="294"/>
+      <c r="I29" s="294"/>
+      <c r="J29" s="294" t="s">
+        <v>28</v>
+      </c>
+      <c r="K29" s="294"/>
+      <c r="L29" s="294"/>
+      <c r="M29" s="328"/>
+      <c r="N29" s="329"/>
+      <c r="O29" s="329"/>
+      <c r="P29" s="329"/>
+      <c r="Q29" s="329"/>
+      <c r="R29" s="330"/>
       <c r="S29" s="311" t="s">
-        <v>18</v>
-      </c>
-      <c r="T29" s="312"/>
-      <c r="U29" s="313"/>
+        <v>19</v>
+      </c>
+      <c r="T29" s="333"/>
+      <c r="U29" s="334"/>
       <c r="V29" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="131">
         <v>4</v>
       </c>
-      <c r="B30" s="369"/>
-      <c r="C30" s="369"/>
-      <c r="D30" s="369"/>
-      <c r="E30" s="369"/>
-      <c r="F30" s="369"/>
-      <c r="G30" s="369"/>
-      <c r="H30" s="370"/>
-      <c r="I30" s="370"/>
-      <c r="J30" s="370" t="s">
-        <v>27</v>
-      </c>
-      <c r="K30" s="370"/>
-      <c r="L30" s="370"/>
-      <c r="M30" s="305"/>
-      <c r="N30" s="306"/>
-      <c r="O30" s="306"/>
-      <c r="P30" s="306"/>
-      <c r="Q30" s="306"/>
-      <c r="R30" s="307"/>
+      <c r="B30" s="291"/>
+      <c r="C30" s="291"/>
+      <c r="D30" s="291"/>
+      <c r="E30" s="291"/>
+      <c r="F30" s="291"/>
+      <c r="G30" s="291"/>
+      <c r="H30" s="292"/>
+      <c r="I30" s="292"/>
+      <c r="J30" s="292" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" s="292"/>
+      <c r="L30" s="292"/>
+      <c r="M30" s="328"/>
+      <c r="N30" s="329"/>
+      <c r="O30" s="329"/>
+      <c r="P30" s="329"/>
+      <c r="Q30" s="329"/>
+      <c r="R30" s="330"/>
       <c r="S30" s="311" t="s">
-        <v>18</v>
-      </c>
-      <c r="T30" s="312"/>
-      <c r="U30" s="313"/>
+        <v>19</v>
+      </c>
+      <c r="T30" s="333"/>
+      <c r="U30" s="334"/>
       <c r="V30" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="137">
         <v>5</v>
       </c>
-      <c r="B31" s="408" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="408"/>
-      <c r="D31" s="408"/>
-      <c r="E31" s="408"/>
-      <c r="F31" s="408"/>
-      <c r="G31" s="408"/>
-      <c r="H31" s="409"/>
-      <c r="I31" s="409"/>
-      <c r="J31" s="409"/>
-      <c r="K31" s="409"/>
-      <c r="L31" s="409"/>
-      <c r="M31" s="317"/>
-      <c r="N31" s="318"/>
-      <c r="O31" s="318"/>
-      <c r="P31" s="318"/>
-      <c r="Q31" s="318"/>
-      <c r="R31" s="319"/>
-      <c r="S31" s="314"/>
-      <c r="T31" s="315"/>
-      <c r="U31" s="316"/>
+      <c r="B31" s="288" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="288"/>
+      <c r="D31" s="288"/>
+      <c r="E31" s="288"/>
+      <c r="F31" s="288"/>
+      <c r="G31" s="288"/>
+      <c r="H31" s="286"/>
+      <c r="I31" s="286"/>
+      <c r="J31" s="286"/>
+      <c r="K31" s="286"/>
+      <c r="L31" s="286"/>
+      <c r="M31" s="375"/>
+      <c r="N31" s="376"/>
+      <c r="O31" s="376"/>
+      <c r="P31" s="376"/>
+      <c r="Q31" s="376"/>
+      <c r="R31" s="377"/>
+      <c r="S31" s="389"/>
+      <c r="T31" s="373"/>
+      <c r="U31" s="374"/>
       <c r="V31" s="138" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:22" s="61" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11211,7 +11038,7 @@
     </row>
     <row r="33" spans="1:22" s="61" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -11237,26 +11064,26 @@
     <row r="34" spans="1:22" s="61" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="F34" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
       <c r="J34" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="L34" s="10"/>
       <c r="M34" s="3"/>
@@ -11294,200 +11121,200 @@
     </row>
     <row r="36" spans="1:22" s="61" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="303" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="304"/>
-      <c r="D36" s="304"/>
-      <c r="E36" s="304"/>
-      <c r="F36" s="206"/>
-      <c r="G36" s="303" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="287" t="s">
         <v>30</v>
       </c>
-      <c r="H36" s="205"/>
-      <c r="I36" s="205"/>
-      <c r="J36" s="303" t="s">
-        <v>97</v>
-      </c>
-      <c r="K36" s="205"/>
-      <c r="L36" s="205"/>
-      <c r="M36" s="205"/>
-      <c r="N36" s="206"/>
-      <c r="O36" s="303" t="s">
-        <v>77</v>
-      </c>
-      <c r="P36" s="205"/>
-      <c r="Q36" s="205"/>
-      <c r="R36" s="205"/>
-      <c r="S36" s="205"/>
-      <c r="T36" s="205"/>
-      <c r="U36" s="206"/>
+      <c r="C36" s="289"/>
+      <c r="D36" s="289"/>
+      <c r="E36" s="289"/>
+      <c r="F36" s="265"/>
+      <c r="G36" s="287" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="264"/>
+      <c r="I36" s="264"/>
+      <c r="J36" s="287" t="s">
+        <v>87</v>
+      </c>
+      <c r="K36" s="264"/>
+      <c r="L36" s="264"/>
+      <c r="M36" s="264"/>
+      <c r="N36" s="265"/>
+      <c r="O36" s="287" t="s">
+        <v>67</v>
+      </c>
+      <c r="P36" s="264"/>
+      <c r="Q36" s="264"/>
+      <c r="R36" s="264"/>
+      <c r="S36" s="264"/>
+      <c r="T36" s="264"/>
+      <c r="U36" s="265"/>
       <c r="V36" s="91" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="130">
         <v>1</v>
       </c>
-      <c r="B37" s="219"/>
-      <c r="C37" s="362"/>
-      <c r="D37" s="362"/>
-      <c r="E37" s="362"/>
-      <c r="F37" s="210"/>
-      <c r="G37" s="219"/>
-      <c r="H37" s="209"/>
-      <c r="I37" s="209"/>
-      <c r="J37" s="222"/>
-      <c r="K37" s="223"/>
-      <c r="L37" s="223"/>
-      <c r="M37" s="223"/>
-      <c r="N37" s="224"/>
-      <c r="O37" s="355"/>
-      <c r="P37" s="209"/>
-      <c r="Q37" s="209"/>
-      <c r="R37" s="209"/>
-      <c r="S37" s="209"/>
-      <c r="T37" s="209"/>
-      <c r="U37" s="210"/>
+      <c r="B37" s="240"/>
+      <c r="C37" s="290"/>
+      <c r="D37" s="290"/>
+      <c r="E37" s="290"/>
+      <c r="F37" s="242"/>
+      <c r="G37" s="240"/>
+      <c r="H37" s="241"/>
+      <c r="I37" s="241"/>
+      <c r="J37" s="270"/>
+      <c r="K37" s="271"/>
+      <c r="L37" s="271"/>
+      <c r="M37" s="271"/>
+      <c r="N37" s="272"/>
+      <c r="O37" s="317"/>
+      <c r="P37" s="241"/>
+      <c r="Q37" s="241"/>
+      <c r="R37" s="241"/>
+      <c r="S37" s="241"/>
+      <c r="T37" s="241"/>
+      <c r="U37" s="242"/>
       <c r="V37" s="133" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="131">
         <v>2</v>
       </c>
-      <c r="B38" s="207"/>
-      <c r="C38" s="344"/>
-      <c r="D38" s="344"/>
-      <c r="E38" s="344"/>
-      <c r="F38" s="187"/>
-      <c r="G38" s="207"/>
-      <c r="H38" s="186"/>
-      <c r="I38" s="187"/>
-      <c r="J38" s="228"/>
-      <c r="K38" s="189"/>
-      <c r="L38" s="189"/>
-      <c r="M38" s="189"/>
-      <c r="N38" s="190"/>
+      <c r="B38" s="243"/>
+      <c r="C38" s="305"/>
+      <c r="D38" s="305"/>
+      <c r="E38" s="305"/>
+      <c r="F38" s="244"/>
+      <c r="G38" s="243"/>
+      <c r="H38" s="239"/>
+      <c r="I38" s="244"/>
+      <c r="J38" s="229"/>
+      <c r="K38" s="230"/>
+      <c r="L38" s="230"/>
+      <c r="M38" s="230"/>
+      <c r="N38" s="231"/>
       <c r="O38" s="311"/>
-      <c r="P38" s="186"/>
-      <c r="Q38" s="186"/>
-      <c r="R38" s="186"/>
-      <c r="S38" s="186"/>
-      <c r="T38" s="186"/>
-      <c r="U38" s="187"/>
+      <c r="P38" s="239"/>
+      <c r="Q38" s="239"/>
+      <c r="R38" s="239"/>
+      <c r="S38" s="239"/>
+      <c r="T38" s="239"/>
+      <c r="U38" s="244"/>
       <c r="V38" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="131">
         <v>3</v>
       </c>
-      <c r="B39" s="207"/>
-      <c r="C39" s="344"/>
-      <c r="D39" s="344"/>
-      <c r="E39" s="344"/>
-      <c r="F39" s="187"/>
-      <c r="G39" s="207"/>
-      <c r="H39" s="186"/>
-      <c r="I39" s="187"/>
-      <c r="J39" s="228"/>
-      <c r="K39" s="189"/>
-      <c r="L39" s="189"/>
-      <c r="M39" s="189"/>
-      <c r="N39" s="190"/>
+      <c r="B39" s="243"/>
+      <c r="C39" s="305"/>
+      <c r="D39" s="305"/>
+      <c r="E39" s="305"/>
+      <c r="F39" s="244"/>
+      <c r="G39" s="243"/>
+      <c r="H39" s="239"/>
+      <c r="I39" s="244"/>
+      <c r="J39" s="229"/>
+      <c r="K39" s="230"/>
+      <c r="L39" s="230"/>
+      <c r="M39" s="230"/>
+      <c r="N39" s="231"/>
       <c r="O39" s="311"/>
-      <c r="P39" s="186"/>
-      <c r="Q39" s="186"/>
-      <c r="R39" s="186"/>
-      <c r="S39" s="186"/>
-      <c r="T39" s="186"/>
-      <c r="U39" s="187"/>
+      <c r="P39" s="239"/>
+      <c r="Q39" s="239"/>
+      <c r="R39" s="239"/>
+      <c r="S39" s="239"/>
+      <c r="T39" s="239"/>
+      <c r="U39" s="244"/>
       <c r="V39" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="131">
         <v>4</v>
       </c>
-      <c r="B40" s="207"/>
-      <c r="C40" s="344"/>
-      <c r="D40" s="344"/>
-      <c r="E40" s="344"/>
-      <c r="F40" s="187"/>
-      <c r="G40" s="207"/>
-      <c r="H40" s="186"/>
-      <c r="I40" s="187"/>
-      <c r="J40" s="228"/>
-      <c r="K40" s="189"/>
-      <c r="L40" s="189"/>
-      <c r="M40" s="189"/>
-      <c r="N40" s="190"/>
+      <c r="B40" s="243"/>
+      <c r="C40" s="305"/>
+      <c r="D40" s="305"/>
+      <c r="E40" s="305"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="243"/>
+      <c r="H40" s="239"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="229"/>
+      <c r="K40" s="230"/>
+      <c r="L40" s="230"/>
+      <c r="M40" s="230"/>
+      <c r="N40" s="231"/>
       <c r="O40" s="311"/>
-      <c r="P40" s="186"/>
-      <c r="Q40" s="186"/>
-      <c r="R40" s="186"/>
-      <c r="S40" s="186"/>
-      <c r="T40" s="186"/>
-      <c r="U40" s="187"/>
+      <c r="P40" s="239"/>
+      <c r="Q40" s="239"/>
+      <c r="R40" s="239"/>
+      <c r="S40" s="239"/>
+      <c r="T40" s="239"/>
+      <c r="U40" s="244"/>
       <c r="V40" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="132">
         <v>5</v>
       </c>
-      <c r="B41" s="200"/>
-      <c r="C41" s="347"/>
-      <c r="D41" s="347"/>
-      <c r="E41" s="347"/>
-      <c r="F41" s="201"/>
-      <c r="G41" s="200"/>
-      <c r="H41" s="192"/>
-      <c r="I41" s="201"/>
-      <c r="J41" s="243"/>
-      <c r="K41" s="244"/>
-      <c r="L41" s="244"/>
-      <c r="M41" s="244"/>
-      <c r="N41" s="245"/>
-      <c r="O41" s="200"/>
-      <c r="P41" s="192"/>
-      <c r="Q41" s="192"/>
-      <c r="R41" s="192"/>
-      <c r="S41" s="192"/>
-      <c r="T41" s="192"/>
-      <c r="U41" s="201"/>
+      <c r="B41" s="226"/>
+      <c r="C41" s="360"/>
+      <c r="D41" s="360"/>
+      <c r="E41" s="360"/>
+      <c r="F41" s="228"/>
+      <c r="G41" s="226"/>
+      <c r="H41" s="227"/>
+      <c r="I41" s="228"/>
+      <c r="J41" s="223"/>
+      <c r="K41" s="224"/>
+      <c r="L41" s="224"/>
+      <c r="M41" s="224"/>
+      <c r="N41" s="225"/>
+      <c r="O41" s="226"/>
+      <c r="P41" s="227"/>
+      <c r="Q41" s="227"/>
+      <c r="R41" s="227"/>
+      <c r="S41" s="227"/>
+      <c r="T41" s="227"/>
+      <c r="U41" s="228"/>
       <c r="V41" s="135" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:22" s="61" customFormat="1" ht="26.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="335" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="336"/>
-      <c r="C42" s="336"/>
-      <c r="D42" s="336"/>
-      <c r="E42" s="336"/>
-      <c r="F42" s="336"/>
-      <c r="G42" s="336"/>
-      <c r="H42" s="336"/>
-      <c r="I42" s="336"/>
-      <c r="J42" s="348">
+      <c r="A42" s="383" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="384"/>
+      <c r="C42" s="384"/>
+      <c r="D42" s="384"/>
+      <c r="E42" s="384"/>
+      <c r="F42" s="384"/>
+      <c r="G42" s="384"/>
+      <c r="H42" s="384"/>
+      <c r="I42" s="384"/>
+      <c r="J42" s="361">
         <f>SUM(J36:J41)</f>
         <v>0</v>
       </c>
-      <c r="K42" s="148"/>
-      <c r="L42" s="148"/>
-      <c r="M42" s="148"/>
-      <c r="N42" s="149"/>
+      <c r="K42" s="249"/>
+      <c r="L42" s="249"/>
+      <c r="M42" s="249"/>
+      <c r="N42" s="250"/>
       <c r="O42" s="92"/>
       <c r="P42" s="92"/>
       <c r="Q42" s="92"/>
@@ -11544,7 +11371,7 @@
     </row>
     <row r="45" spans="1:22" s="61" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -11570,26 +11397,26 @@
     <row r="46" spans="1:22" s="61" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10"/>
       <c r="B46" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
       <c r="F46" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K46" s="12" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="L46" s="10"/>
       <c r="M46" s="3"/>
@@ -11627,178 +11454,178 @@
     </row>
     <row r="48" spans="1:22" s="61" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="337" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" s="337"/>
-      <c r="D48" s="337"/>
-      <c r="E48" s="337"/>
-      <c r="F48" s="303" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="385" t="s">
         <v>34</v>
       </c>
-      <c r="G48" s="304"/>
-      <c r="H48" s="304"/>
-      <c r="I48" s="206"/>
-      <c r="J48" s="303" t="s">
-        <v>98</v>
-      </c>
-      <c r="K48" s="304"/>
-      <c r="L48" s="304"/>
-      <c r="M48" s="304"/>
-      <c r="N48" s="206"/>
-      <c r="O48" s="303" t="s">
-        <v>77</v>
-      </c>
-      <c r="P48" s="205"/>
-      <c r="Q48" s="205"/>
-      <c r="R48" s="205"/>
-      <c r="S48" s="205"/>
-      <c r="T48" s="205"/>
-      <c r="U48" s="206"/>
+      <c r="C48" s="385"/>
+      <c r="D48" s="385"/>
+      <c r="E48" s="385"/>
+      <c r="F48" s="287" t="s">
+        <v>35</v>
+      </c>
+      <c r="G48" s="289"/>
+      <c r="H48" s="289"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="287" t="s">
+        <v>88</v>
+      </c>
+      <c r="K48" s="289"/>
+      <c r="L48" s="289"/>
+      <c r="M48" s="289"/>
+      <c r="N48" s="265"/>
+      <c r="O48" s="287" t="s">
+        <v>67</v>
+      </c>
+      <c r="P48" s="264"/>
+      <c r="Q48" s="264"/>
+      <c r="R48" s="264"/>
+      <c r="S48" s="264"/>
+      <c r="T48" s="264"/>
+      <c r="U48" s="265"/>
       <c r="V48" s="91" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="130">
         <v>1</v>
       </c>
-      <c r="B49" s="333"/>
-      <c r="C49" s="333"/>
-      <c r="D49" s="333"/>
-      <c r="E49" s="333"/>
-      <c r="F49" s="256"/>
-      <c r="G49" s="343"/>
-      <c r="H49" s="343"/>
-      <c r="I49" s="258"/>
-      <c r="J49" s="222"/>
-      <c r="K49" s="352"/>
-      <c r="L49" s="352"/>
-      <c r="M49" s="352"/>
-      <c r="N49" s="357"/>
-      <c r="O49" s="355"/>
-      <c r="P49" s="209"/>
-      <c r="Q49" s="209"/>
-      <c r="R49" s="209"/>
-      <c r="S49" s="209"/>
-      <c r="T49" s="209"/>
-      <c r="U49" s="210"/>
+      <c r="B49" s="381"/>
+      <c r="C49" s="381"/>
+      <c r="D49" s="381"/>
+      <c r="E49" s="381"/>
+      <c r="F49" s="206"/>
+      <c r="G49" s="388"/>
+      <c r="H49" s="388"/>
+      <c r="I49" s="208"/>
+      <c r="J49" s="270"/>
+      <c r="K49" s="316"/>
+      <c r="L49" s="316"/>
+      <c r="M49" s="316"/>
+      <c r="N49" s="362"/>
+      <c r="O49" s="317"/>
+      <c r="P49" s="241"/>
+      <c r="Q49" s="241"/>
+      <c r="R49" s="241"/>
+      <c r="S49" s="241"/>
+      <c r="T49" s="241"/>
+      <c r="U49" s="242"/>
       <c r="V49" s="133" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="131">
         <v>2</v>
       </c>
-      <c r="B50" s="334"/>
-      <c r="C50" s="334"/>
-      <c r="D50" s="334"/>
-      <c r="E50" s="334"/>
-      <c r="F50" s="207"/>
-      <c r="G50" s="344"/>
-      <c r="H50" s="344"/>
-      <c r="I50" s="187"/>
-      <c r="J50" s="228"/>
-      <c r="K50" s="350"/>
-      <c r="L50" s="350"/>
-      <c r="M50" s="350"/>
-      <c r="N50" s="358"/>
+      <c r="B50" s="382"/>
+      <c r="C50" s="382"/>
+      <c r="D50" s="382"/>
+      <c r="E50" s="382"/>
+      <c r="F50" s="243"/>
+      <c r="G50" s="305"/>
+      <c r="H50" s="305"/>
+      <c r="I50" s="244"/>
+      <c r="J50" s="229"/>
+      <c r="K50" s="309"/>
+      <c r="L50" s="309"/>
+      <c r="M50" s="309"/>
+      <c r="N50" s="310"/>
       <c r="O50" s="311"/>
-      <c r="P50" s="186"/>
-      <c r="Q50" s="186"/>
-      <c r="R50" s="186"/>
-      <c r="S50" s="186"/>
-      <c r="T50" s="186"/>
-      <c r="U50" s="187"/>
+      <c r="P50" s="239"/>
+      <c r="Q50" s="239"/>
+      <c r="R50" s="239"/>
+      <c r="S50" s="239"/>
+      <c r="T50" s="239"/>
+      <c r="U50" s="244"/>
       <c r="V50" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="131">
         <v>3</v>
       </c>
-      <c r="B51" s="339"/>
-      <c r="C51" s="339"/>
-      <c r="D51" s="339"/>
-      <c r="E51" s="339"/>
-      <c r="F51" s="207"/>
-      <c r="G51" s="344"/>
-      <c r="H51" s="344"/>
-      <c r="I51" s="187"/>
-      <c r="J51" s="228"/>
-      <c r="K51" s="350"/>
-      <c r="L51" s="350"/>
-      <c r="M51" s="350"/>
-      <c r="N51" s="358"/>
+      <c r="B51" s="387"/>
+      <c r="C51" s="387"/>
+      <c r="D51" s="387"/>
+      <c r="E51" s="387"/>
+      <c r="F51" s="243"/>
+      <c r="G51" s="305"/>
+      <c r="H51" s="305"/>
+      <c r="I51" s="244"/>
+      <c r="J51" s="229"/>
+      <c r="K51" s="309"/>
+      <c r="L51" s="309"/>
+      <c r="M51" s="309"/>
+      <c r="N51" s="310"/>
       <c r="O51" s="311"/>
-      <c r="P51" s="186"/>
-      <c r="Q51" s="186"/>
-      <c r="R51" s="186"/>
-      <c r="S51" s="186"/>
-      <c r="T51" s="186"/>
-      <c r="U51" s="187"/>
+      <c r="P51" s="239"/>
+      <c r="Q51" s="239"/>
+      <c r="R51" s="239"/>
+      <c r="S51" s="239"/>
+      <c r="T51" s="239"/>
+      <c r="U51" s="244"/>
       <c r="V51" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="131">
         <v>4</v>
       </c>
-      <c r="B52" s="339"/>
-      <c r="C52" s="339"/>
-      <c r="D52" s="339"/>
-      <c r="E52" s="339"/>
-      <c r="F52" s="207"/>
-      <c r="G52" s="344"/>
-      <c r="H52" s="344"/>
-      <c r="I52" s="187"/>
-      <c r="J52" s="228"/>
-      <c r="K52" s="350"/>
-      <c r="L52" s="350"/>
-      <c r="M52" s="350"/>
-      <c r="N52" s="358"/>
+      <c r="B52" s="387"/>
+      <c r="C52" s="387"/>
+      <c r="D52" s="387"/>
+      <c r="E52" s="387"/>
+      <c r="F52" s="243"/>
+      <c r="G52" s="305"/>
+      <c r="H52" s="305"/>
+      <c r="I52" s="244"/>
+      <c r="J52" s="229"/>
+      <c r="K52" s="309"/>
+      <c r="L52" s="309"/>
+      <c r="M52" s="309"/>
+      <c r="N52" s="310"/>
       <c r="O52" s="311"/>
-      <c r="P52" s="186"/>
-      <c r="Q52" s="186"/>
-      <c r="R52" s="186"/>
-      <c r="S52" s="186"/>
-      <c r="T52" s="186"/>
-      <c r="U52" s="187"/>
+      <c r="P52" s="239"/>
+      <c r="Q52" s="239"/>
+      <c r="R52" s="239"/>
+      <c r="S52" s="239"/>
+      <c r="T52" s="239"/>
+      <c r="U52" s="244"/>
       <c r="V52" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="137">
         <v>5</v>
       </c>
-      <c r="B53" s="338"/>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="340"/>
-      <c r="G53" s="341"/>
-      <c r="H53" s="341"/>
-      <c r="I53" s="342"/>
-      <c r="J53" s="359"/>
-      <c r="K53" s="360"/>
-      <c r="L53" s="360"/>
-      <c r="M53" s="360"/>
-      <c r="N53" s="361"/>
-      <c r="O53" s="340"/>
-      <c r="P53" s="356"/>
-      <c r="Q53" s="356"/>
-      <c r="R53" s="356"/>
-      <c r="S53" s="356"/>
-      <c r="T53" s="356"/>
-      <c r="U53" s="342"/>
+      <c r="B53" s="386"/>
+      <c r="C53" s="386"/>
+      <c r="D53" s="386"/>
+      <c r="E53" s="386"/>
+      <c r="F53" s="342"/>
+      <c r="G53" s="343"/>
+      <c r="H53" s="343"/>
+      <c r="I53" s="356"/>
+      <c r="J53" s="347"/>
+      <c r="K53" s="348"/>
+      <c r="L53" s="348"/>
+      <c r="M53" s="348"/>
+      <c r="N53" s="349"/>
+      <c r="O53" s="342"/>
+      <c r="P53" s="355"/>
+      <c r="Q53" s="355"/>
+      <c r="R53" s="355"/>
+      <c r="S53" s="355"/>
+      <c r="T53" s="355"/>
+      <c r="U53" s="356"/>
       <c r="V53" s="138" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:22" s="61" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -11825,7 +11652,7 @@
     </row>
     <row r="55" spans="1:22" s="61" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -11851,26 +11678,26 @@
     <row r="56" spans="1:22" s="61" customFormat="1" ht="14.4" x14ac:dyDescent="0.2">
       <c r="A56" s="10"/>
       <c r="B56" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
       <c r="F56" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H56" s="10"/>
       <c r="I56" s="10"/>
       <c r="J56" s="86" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56" s="12" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="L56" s="10"/>
       <c r="M56" s="3"/>
@@ -11908,210 +11735,210 @@
     </row>
     <row r="58" spans="1:22" s="61" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="87" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B58" s="366" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C58" s="367"/>
       <c r="D58" s="367"/>
       <c r="E58" s="367"/>
       <c r="F58" s="368"/>
-      <c r="G58" s="303" t="s">
-        <v>37</v>
-      </c>
-      <c r="H58" s="205"/>
-      <c r="I58" s="205"/>
-      <c r="J58" s="205"/>
-      <c r="K58" s="303" t="s">
-        <v>97</v>
-      </c>
-      <c r="L58" s="304"/>
-      <c r="M58" s="304"/>
-      <c r="N58" s="304"/>
-      <c r="O58" s="304"/>
-      <c r="P58" s="206"/>
-      <c r="Q58" s="303" t="s">
-        <v>99</v>
-      </c>
-      <c r="R58" s="205"/>
-      <c r="S58" s="205"/>
-      <c r="T58" s="205"/>
-      <c r="U58" s="206"/>
+      <c r="G58" s="287" t="s">
+        <v>38</v>
+      </c>
+      <c r="H58" s="264"/>
+      <c r="I58" s="264"/>
+      <c r="J58" s="264"/>
+      <c r="K58" s="287" t="s">
+        <v>87</v>
+      </c>
+      <c r="L58" s="289"/>
+      <c r="M58" s="289"/>
+      <c r="N58" s="289"/>
+      <c r="O58" s="289"/>
+      <c r="P58" s="265"/>
+      <c r="Q58" s="287" t="s">
+        <v>89</v>
+      </c>
+      <c r="R58" s="264"/>
+      <c r="S58" s="264"/>
+      <c r="T58" s="264"/>
+      <c r="U58" s="265"/>
       <c r="V58" s="91" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="130">
         <v>1</v>
       </c>
-      <c r="B59" s="219"/>
-      <c r="C59" s="362"/>
-      <c r="D59" s="362"/>
-      <c r="E59" s="362"/>
-      <c r="F59" s="210"/>
-      <c r="G59" s="219"/>
-      <c r="H59" s="209"/>
-      <c r="I59" s="209"/>
-      <c r="J59" s="210"/>
-      <c r="K59" s="222"/>
-      <c r="L59" s="352"/>
-      <c r="M59" s="352"/>
-      <c r="N59" s="352"/>
-      <c r="O59" s="352"/>
-      <c r="P59" s="223"/>
+      <c r="B59" s="240"/>
+      <c r="C59" s="290"/>
+      <c r="D59" s="290"/>
+      <c r="E59" s="290"/>
+      <c r="F59" s="242"/>
+      <c r="G59" s="240"/>
+      <c r="H59" s="241"/>
+      <c r="I59" s="241"/>
+      <c r="J59" s="242"/>
+      <c r="K59" s="270"/>
+      <c r="L59" s="316"/>
+      <c r="M59" s="316"/>
+      <c r="N59" s="316"/>
+      <c r="O59" s="316"/>
+      <c r="P59" s="271"/>
       <c r="Q59" s="363"/>
       <c r="R59" s="364"/>
       <c r="S59" s="364"/>
       <c r="T59" s="364"/>
       <c r="U59" s="365"/>
       <c r="V59" s="133" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="131">
         <v>2</v>
       </c>
-      <c r="B60" s="207"/>
-      <c r="C60" s="344"/>
-      <c r="D60" s="344"/>
-      <c r="E60" s="344"/>
-      <c r="F60" s="187"/>
-      <c r="G60" s="207" t="s">
-        <v>18</v>
-      </c>
-      <c r="H60" s="186"/>
-      <c r="I60" s="186"/>
-      <c r="J60" s="187"/>
-      <c r="K60" s="228"/>
-      <c r="L60" s="350"/>
-      <c r="M60" s="350"/>
-      <c r="N60" s="350"/>
-      <c r="O60" s="350"/>
-      <c r="P60" s="189"/>
-      <c r="Q60" s="327"/>
-      <c r="R60" s="328"/>
-      <c r="S60" s="328"/>
-      <c r="T60" s="328"/>
-      <c r="U60" s="329"/>
+      <c r="B60" s="243"/>
+      <c r="C60" s="305"/>
+      <c r="D60" s="305"/>
+      <c r="E60" s="305"/>
+      <c r="F60" s="244"/>
+      <c r="G60" s="243" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" s="239"/>
+      <c r="I60" s="239"/>
+      <c r="J60" s="244"/>
+      <c r="K60" s="229"/>
+      <c r="L60" s="309"/>
+      <c r="M60" s="309"/>
+      <c r="N60" s="309"/>
+      <c r="O60" s="309"/>
+      <c r="P60" s="230"/>
+      <c r="Q60" s="282"/>
+      <c r="R60" s="283"/>
+      <c r="S60" s="283"/>
+      <c r="T60" s="283"/>
+      <c r="U60" s="284"/>
       <c r="V60" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="131">
         <v>3</v>
       </c>
-      <c r="B61" s="207"/>
-      <c r="C61" s="344"/>
-      <c r="D61" s="344"/>
-      <c r="E61" s="344"/>
-      <c r="F61" s="187"/>
-      <c r="G61" s="207" t="s">
-        <v>18</v>
-      </c>
-      <c r="H61" s="186"/>
-      <c r="I61" s="186"/>
-      <c r="J61" s="187"/>
-      <c r="K61" s="228"/>
-      <c r="L61" s="350"/>
-      <c r="M61" s="350"/>
-      <c r="N61" s="350"/>
-      <c r="O61" s="350"/>
-      <c r="P61" s="189"/>
-      <c r="Q61" s="327"/>
-      <c r="R61" s="328"/>
-      <c r="S61" s="328"/>
-      <c r="T61" s="328"/>
-      <c r="U61" s="329"/>
+      <c r="B61" s="243"/>
+      <c r="C61" s="305"/>
+      <c r="D61" s="305"/>
+      <c r="E61" s="305"/>
+      <c r="F61" s="244"/>
+      <c r="G61" s="243" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" s="239"/>
+      <c r="I61" s="239"/>
+      <c r="J61" s="244"/>
+      <c r="K61" s="229"/>
+      <c r="L61" s="309"/>
+      <c r="M61" s="309"/>
+      <c r="N61" s="309"/>
+      <c r="O61" s="309"/>
+      <c r="P61" s="230"/>
+      <c r="Q61" s="282"/>
+      <c r="R61" s="283"/>
+      <c r="S61" s="283"/>
+      <c r="T61" s="283"/>
+      <c r="U61" s="284"/>
       <c r="V61" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="131">
         <v>4</v>
       </c>
-      <c r="B62" s="207"/>
-      <c r="C62" s="344"/>
-      <c r="D62" s="344"/>
-      <c r="E62" s="344"/>
-      <c r="F62" s="187"/>
-      <c r="G62" s="207" t="s">
-        <v>18</v>
-      </c>
-      <c r="H62" s="186"/>
-      <c r="I62" s="186"/>
-      <c r="J62" s="187"/>
-      <c r="K62" s="228"/>
-      <c r="L62" s="350"/>
-      <c r="M62" s="350"/>
-      <c r="N62" s="350"/>
-      <c r="O62" s="350"/>
-      <c r="P62" s="189"/>
-      <c r="Q62" s="327"/>
-      <c r="R62" s="328"/>
-      <c r="S62" s="328"/>
-      <c r="T62" s="328"/>
-      <c r="U62" s="329"/>
+      <c r="B62" s="243"/>
+      <c r="C62" s="305"/>
+      <c r="D62" s="305"/>
+      <c r="E62" s="305"/>
+      <c r="F62" s="244"/>
+      <c r="G62" s="243" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" s="239"/>
+      <c r="I62" s="239"/>
+      <c r="J62" s="244"/>
+      <c r="K62" s="229"/>
+      <c r="L62" s="309"/>
+      <c r="M62" s="309"/>
+      <c r="N62" s="309"/>
+      <c r="O62" s="309"/>
+      <c r="P62" s="230"/>
+      <c r="Q62" s="282"/>
+      <c r="R62" s="283"/>
+      <c r="S62" s="283"/>
+      <c r="T62" s="283"/>
+      <c r="U62" s="284"/>
       <c r="V62" s="134" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:22" s="96" customFormat="1" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="132">
         <v>5</v>
       </c>
-      <c r="B63" s="200"/>
-      <c r="C63" s="347"/>
-      <c r="D63" s="347"/>
-      <c r="E63" s="347"/>
-      <c r="F63" s="201"/>
+      <c r="B63" s="226"/>
+      <c r="C63" s="360"/>
+      <c r="D63" s="360"/>
+      <c r="E63" s="360"/>
+      <c r="F63" s="228"/>
       <c r="G63" s="143"/>
       <c r="H63" s="146"/>
       <c r="I63" s="146"/>
       <c r="J63" s="144"/>
-      <c r="K63" s="243" t="s">
-        <v>18</v>
-      </c>
-      <c r="L63" s="351"/>
-      <c r="M63" s="351"/>
-      <c r="N63" s="351"/>
-      <c r="O63" s="351"/>
-      <c r="P63" s="244"/>
-      <c r="Q63" s="330"/>
-      <c r="R63" s="331"/>
-      <c r="S63" s="331"/>
-      <c r="T63" s="331"/>
-      <c r="U63" s="332"/>
+      <c r="K63" s="223" t="s">
+        <v>19</v>
+      </c>
+      <c r="L63" s="370"/>
+      <c r="M63" s="370"/>
+      <c r="N63" s="370"/>
+      <c r="O63" s="370"/>
+      <c r="P63" s="224"/>
+      <c r="Q63" s="378"/>
+      <c r="R63" s="379"/>
+      <c r="S63" s="379"/>
+      <c r="T63" s="379"/>
+      <c r="U63" s="380"/>
       <c r="V63" s="135" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:22" s="61" customFormat="1" ht="26.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="353" t="s">
-        <v>31</v>
-      </c>
-      <c r="B64" s="354"/>
-      <c r="C64" s="354"/>
-      <c r="D64" s="354"/>
-      <c r="E64" s="354"/>
-      <c r="F64" s="354"/>
-      <c r="G64" s="354"/>
-      <c r="H64" s="354"/>
-      <c r="I64" s="354"/>
+      <c r="A64" s="371" t="s">
+        <v>32</v>
+      </c>
+      <c r="B64" s="372"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
+      <c r="G64" s="372"/>
+      <c r="H64" s="372"/>
+      <c r="I64" s="372"/>
       <c r="J64" s="93"/>
-      <c r="K64" s="348">
+      <c r="K64" s="361">
         <f>SUM(K58:K63)</f>
         <v>0</v>
       </c>
-      <c r="L64" s="349"/>
-      <c r="M64" s="349"/>
-      <c r="N64" s="349"/>
-      <c r="O64" s="349"/>
-      <c r="P64" s="149"/>
+      <c r="L64" s="369"/>
+      <c r="M64" s="369"/>
+      <c r="N64" s="369"/>
+      <c r="O64" s="369"/>
+      <c r="P64" s="250"/>
       <c r="Q64" s="136"/>
       <c r="R64" s="101"/>
       <c r="S64" s="101"/>
@@ -12144,7 +11971,7 @@
     </row>
     <row r="66" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -12170,10 +11997,10 @@
     </row>
     <row r="67" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="95" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
@@ -12197,10 +12024,10 @@
     </row>
     <row r="68" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="95" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
@@ -12224,10 +12051,10 @@
     </row>
     <row r="69" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B69" s="95" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
@@ -12252,6 +12079,153 @@
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatRows="0" insertRows="0" deleteRows="0"/>
   <mergeCells count="171">
+    <mergeCell ref="M26:R26"/>
+    <mergeCell ref="M28:R28"/>
+    <mergeCell ref="M29:R29"/>
+    <mergeCell ref="M30:R30"/>
+    <mergeCell ref="S26:U26"/>
+    <mergeCell ref="S29:U29"/>
+    <mergeCell ref="S30:U30"/>
+    <mergeCell ref="S31:U31"/>
+    <mergeCell ref="M31:R31"/>
+    <mergeCell ref="M27:R27"/>
+    <mergeCell ref="S27:U27"/>
+    <mergeCell ref="S28:U28"/>
+    <mergeCell ref="S19:U19"/>
+    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="S21:U21"/>
+    <mergeCell ref="M21:R21"/>
+    <mergeCell ref="M19:R19"/>
+    <mergeCell ref="M20:R20"/>
+    <mergeCell ref="Q62:U62"/>
+    <mergeCell ref="Q63:U63"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="O41:U41"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="K64:P64"/>
+    <mergeCell ref="G58:J58"/>
+    <mergeCell ref="K61:P61"/>
+    <mergeCell ref="K62:P62"/>
+    <mergeCell ref="K63:P63"/>
+    <mergeCell ref="K58:P58"/>
+    <mergeCell ref="K59:P59"/>
+    <mergeCell ref="K60:P60"/>
+    <mergeCell ref="G59:J59"/>
+    <mergeCell ref="G60:J60"/>
+    <mergeCell ref="G61:J61"/>
+    <mergeCell ref="G62:J62"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="O48:U48"/>
+    <mergeCell ref="J48:N48"/>
+    <mergeCell ref="J42:N42"/>
+    <mergeCell ref="O38:U38"/>
+    <mergeCell ref="O39:U39"/>
+    <mergeCell ref="O40:U40"/>
+    <mergeCell ref="O49:U49"/>
+    <mergeCell ref="O50:U50"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="O51:U51"/>
+    <mergeCell ref="O52:U52"/>
+    <mergeCell ref="O53:U53"/>
+    <mergeCell ref="J49:N49"/>
+    <mergeCell ref="J50:N50"/>
+    <mergeCell ref="J51:N51"/>
+    <mergeCell ref="J52:N52"/>
+    <mergeCell ref="J53:N53"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="Q58:U58"/>
+    <mergeCell ref="Q59:U59"/>
+    <mergeCell ref="Q60:U60"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="O37:U37"/>
+    <mergeCell ref="O36:U36"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="M16:R16"/>
+    <mergeCell ref="M11:S11"/>
+    <mergeCell ref="S16:U16"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="M9:S9"/>
+    <mergeCell ref="M10:S10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="M17:R17"/>
+    <mergeCell ref="M18:R18"/>
+    <mergeCell ref="S17:U17"/>
+    <mergeCell ref="S18:U18"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="M6:S6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="M7:S7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:L20"/>
     <mergeCell ref="Q61:U61"/>
     <mergeCell ref="J27:L27"/>
     <mergeCell ref="G38:I38"/>
@@ -12276,153 +12250,6 @@
     <mergeCell ref="J40:N40"/>
     <mergeCell ref="J41:N41"/>
     <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="M6:S6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="M7:S7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="M17:R17"/>
-    <mergeCell ref="M18:R18"/>
-    <mergeCell ref="S17:U17"/>
-    <mergeCell ref="S18:U18"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="M9:S9"/>
-    <mergeCell ref="M10:S10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="M16:R16"/>
-    <mergeCell ref="M11:S11"/>
-    <mergeCell ref="S16:U16"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="O37:U37"/>
-    <mergeCell ref="O36:U36"/>
-    <mergeCell ref="O48:U48"/>
-    <mergeCell ref="J48:N48"/>
-    <mergeCell ref="J42:N42"/>
-    <mergeCell ref="O38:U38"/>
-    <mergeCell ref="O39:U39"/>
-    <mergeCell ref="O40:U40"/>
-    <mergeCell ref="O49:U49"/>
-    <mergeCell ref="O50:U50"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="O51:U51"/>
-    <mergeCell ref="O52:U52"/>
-    <mergeCell ref="O53:U53"/>
-    <mergeCell ref="J49:N49"/>
-    <mergeCell ref="J50:N50"/>
-    <mergeCell ref="J51:N51"/>
-    <mergeCell ref="J52:N52"/>
-    <mergeCell ref="J53:N53"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="Q58:U58"/>
-    <mergeCell ref="Q59:U59"/>
-    <mergeCell ref="Q60:U60"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="K64:P64"/>
-    <mergeCell ref="G58:J58"/>
-    <mergeCell ref="K61:P61"/>
-    <mergeCell ref="K62:P62"/>
-    <mergeCell ref="K63:P63"/>
-    <mergeCell ref="K58:P58"/>
-    <mergeCell ref="K59:P59"/>
-    <mergeCell ref="K60:P60"/>
-    <mergeCell ref="G59:J59"/>
-    <mergeCell ref="G60:J60"/>
-    <mergeCell ref="G61:J61"/>
-    <mergeCell ref="G62:J62"/>
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="S19:U19"/>
-    <mergeCell ref="S20:U20"/>
-    <mergeCell ref="S21:U21"/>
-    <mergeCell ref="M21:R21"/>
-    <mergeCell ref="M19:R19"/>
-    <mergeCell ref="M20:R20"/>
-    <mergeCell ref="Q62:U62"/>
-    <mergeCell ref="Q63:U63"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="O41:U41"/>
-    <mergeCell ref="M26:R26"/>
-    <mergeCell ref="M28:R28"/>
-    <mergeCell ref="M29:R29"/>
-    <mergeCell ref="M30:R30"/>
-    <mergeCell ref="S26:U26"/>
-    <mergeCell ref="S29:U29"/>
-    <mergeCell ref="S30:U30"/>
-    <mergeCell ref="S31:U31"/>
-    <mergeCell ref="M31:R31"/>
-    <mergeCell ref="M27:R27"/>
-    <mergeCell ref="S27:U27"/>
-    <mergeCell ref="S28:U28"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="4">
